--- a/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7C07CF1-92A8-4A95-96A4-114FE2DB46EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{031D0189-49EB-4FFF-A3D2-95267C367B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4233" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4235" uniqueCount="987">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -757,18 +757,18 @@
     <t>solar resource -- CF class spv-IND_23 -- cost class 1</t>
   </si>
   <si>
+    <t>e_spv-IND_23_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_23 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_spv-IND_23_c3</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_23 -- cost class 3</t>
   </si>
   <si>
-    <t>e_spv-IND_23_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_23 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_spv-IND_23_c5</t>
   </si>
   <si>
@@ -985,6 +985,18 @@
     <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c5</t>
   </si>
   <si>
@@ -997,18 +1009,6 @@
     <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
   </si>
   <si>
-    <t>e_spv-IND_0_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
-  </si>
-  <si>
     <t>comm-out</t>
   </si>
   <si>
@@ -1270,18 +1270,18 @@
     <t>onshore wind resource -- CF class won-IND_34 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-IND_33_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-IND_33 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-IND_33_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-IND_33 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-IND_33_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-IND_33 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-IND_33_c4</t>
   </si>
   <si>
@@ -1318,18 +1318,18 @@
     <t>onshore wind resource -- CF class won-IND_32 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-IND_31_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-IND_31 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-IND_31_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-IND_31 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-IND_31_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-IND_31 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-IND_31_c2</t>
   </si>
   <si>
@@ -1438,18 +1438,18 @@
     <t>onshore wind resource -- CF class won-IND_28 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-IND_27_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-IND_27 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-IND_27_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-IND_27 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-IND_27_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-IND_27 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-IND_27_c2</t>
   </si>
   <si>
@@ -1768,18 +1768,18 @@
     <t>onshore wind resource -- CF class won-IND_17 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-IND_16_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-IND_16 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-IND_16_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-IND_16 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-IND_16_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-IND_16 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-IND_16_c2</t>
   </si>
   <si>
@@ -1804,18 +1804,18 @@
     <t>onshore wind resource -- CF class won-IND_15 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-IND_15_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-IND_15 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-IND_15_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-IND_15 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-IND_15_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-IND_15 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-IND_15_c2</t>
   </si>
   <si>
@@ -1846,18 +1846,18 @@
     <t>onshore wind resource -- CF class won-IND_14 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-IND_14_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-IND_14 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-IND_14_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-IND_14 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-IND_14_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-IND_14 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-IND_13_c3</t>
   </si>
   <si>
@@ -1996,16 +1996,16 @@
     <t>onshore wind resource -- CF class won-IND_9 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-IND_9_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-IND_9 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-IND_9_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-IND_9 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-IND_9_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-IND_9 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-IND_8_c2</t>
@@ -4628,7 +4628,9 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="str">
@@ -4664,7 +4666,9 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
@@ -7946,7 +7950,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DF111D-3899-401F-83EC-27CA287F5ED6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE42652-1440-4710-B690-CA44501A8F26}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8025,10 +8029,10 @@
         <v>297</v>
       </c>
       <c r="L11">
-        <v>45.413249999999998</v>
+        <v>28.958530451961305</v>
       </c>
       <c r="M11">
-        <v>0.24928368307746038</v>
+        <v>0.24917945174153316</v>
       </c>
       <c r="N11">
         <v>4</v>
@@ -8063,10 +8067,10 @@
         <v>297</v>
       </c>
       <c r="L12">
-        <v>45.740250000000003</v>
+        <v>30.42162466670111</v>
       </c>
       <c r="M12">
-        <v>0.24920212315300028</v>
+        <v>0.24915876296678849</v>
       </c>
       <c r="N12">
         <v>2</v>
@@ -8101,10 +8105,10 @@
         <v>297</v>
       </c>
       <c r="L13">
-        <v>45.411000000000001</v>
+        <v>29.856069786390844</v>
       </c>
       <c r="M13">
-        <v>0.24901663350251055</v>
+        <v>0.2489668086269882</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -8139,10 +8143,10 @@
         <v>297</v>
       </c>
       <c r="L14">
-        <v>45.476999999999997</v>
+        <v>30.065612361537205</v>
       </c>
       <c r="M14">
-        <v>0.24772913911132136</v>
+        <v>0.24769498163898618</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -8177,10 +8181,10 @@
         <v>297</v>
       </c>
       <c r="L15">
-        <v>34.006500000000003</v>
+        <v>22.819469850560996</v>
       </c>
       <c r="M15">
-        <v>0.24686329138465565</v>
+        <v>0.24685465814446381</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -8215,10 +8219,10 @@
         <v>297</v>
       </c>
       <c r="L16">
-        <v>61.058999999999997</v>
+        <v>41.175630219180952</v>
       </c>
       <c r="M16">
-        <v>0.24034654265682692</v>
+        <v>0.24038447248958086</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -8253,10 +8257,10 @@
         <v>297</v>
       </c>
       <c r="L17">
-        <v>73.086749999999995</v>
+        <v>49.834583880983949</v>
       </c>
       <c r="M17">
-        <v>0.23976633158566013</v>
+        <v>0.23992289573797695</v>
       </c>
       <c r="N17">
         <v>4</v>
@@ -8291,10 +8295,10 @@
         <v>297</v>
       </c>
       <c r="L18">
-        <v>74.817750000000004</v>
+        <v>49.456312961988999</v>
       </c>
       <c r="M18">
-        <v>0.23954720465574822</v>
+        <v>0.2397010435864321</v>
       </c>
       <c r="N18">
         <v>2</v>
@@ -8329,10 +8333,10 @@
         <v>297</v>
       </c>
       <c r="L19">
-        <v>75.535499999999999</v>
+        <v>48.192884216188311</v>
       </c>
       <c r="M19">
-        <v>0.23846181423550283</v>
+        <v>0.23850760239747584</v>
       </c>
       <c r="N19">
         <v>3</v>
@@ -8367,10 +8371,10 @@
         <v>297</v>
       </c>
       <c r="L20">
-        <v>73.736999999999995</v>
+        <v>55.789938522361702</v>
       </c>
       <c r="M20">
-        <v>0.23817738573304248</v>
+        <v>0.23815798889586362</v>
       </c>
       <c r="N20">
         <v>5</v>
@@ -8405,10 +8409,10 @@
         <v>297</v>
       </c>
       <c r="L21">
-        <v>82.658249999999995</v>
+        <v>61.191076769268946</v>
       </c>
       <c r="M21">
-        <v>0.23057894490382644</v>
+        <v>0.23053832627623169</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -8443,10 +8447,10 @@
         <v>297</v>
       </c>
       <c r="L22">
-        <v>104.94</v>
+        <v>71.024760707563871</v>
       </c>
       <c r="M22">
-        <v>0.22995935708949164</v>
+        <v>0.22990047555325863</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -8481,13 +8485,13 @@
         <v>297</v>
       </c>
       <c r="L23">
-        <v>94.031999999999996</v>
+        <v>71.618521174680893</v>
       </c>
       <c r="M23">
-        <v>0.22940218550665736</v>
+        <v>0.22935761964722812</v>
       </c>
       <c r="N23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="2:14">
@@ -8519,13 +8523,13 @@
         <v>297</v>
       </c>
       <c r="L24">
-        <v>110.99925</v>
+        <v>65.548079321542346</v>
       </c>
       <c r="M24">
-        <v>0.22933879222415093</v>
+        <v>0.22928056924741194</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="2:14">
@@ -8557,10 +8561,10 @@
         <v>297</v>
       </c>
       <c r="L25">
-        <v>102.97199999999999</v>
+        <v>81.57542812168343</v>
       </c>
       <c r="M25">
-        <v>0.22754653619935061</v>
+        <v>0.22756645862357569</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -8595,10 +8599,10 @@
         <v>297</v>
       </c>
       <c r="L26">
-        <v>313.61025000000001</v>
+        <v>210.74711990124698</v>
       </c>
       <c r="M26">
-        <v>0.2212080950557786</v>
+        <v>0.22123398324231208</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -8633,10 +8637,10 @@
         <v>297</v>
       </c>
       <c r="L27">
-        <v>350.12475000000001</v>
+        <v>250.77287171566402</v>
       </c>
       <c r="M27">
-        <v>0.22080282075591576</v>
+        <v>0.22074431360254396</v>
       </c>
       <c r="N27">
         <v>4</v>
@@ -8671,10 +8675,10 @@
         <v>297</v>
       </c>
       <c r="L28">
-        <v>307.33199999999999</v>
+        <v>255.27641914245186</v>
       </c>
       <c r="M28">
-        <v>0.21907242789610154</v>
+        <v>0.21908833044860368</v>
       </c>
       <c r="N28">
         <v>3</v>
@@ -8709,10 +8713,10 @@
         <v>297</v>
       </c>
       <c r="L29">
-        <v>304.90050000000002</v>
+        <v>231.71663184201267</v>
       </c>
       <c r="M29">
-        <v>0.21880912626478333</v>
+        <v>0.21891651044236071</v>
       </c>
       <c r="N29">
         <v>5</v>
@@ -8747,10 +8751,10 @@
         <v>297</v>
       </c>
       <c r="L30">
-        <v>307.22474999999997</v>
+        <v>221.67446666038649</v>
       </c>
       <c r="M30">
-        <v>0.2175358104379862</v>
+        <v>0.21767110949903298</v>
       </c>
       <c r="N30">
         <v>2</v>
@@ -8785,10 +8789,10 @@
         <v>297</v>
       </c>
       <c r="L31">
-        <v>473.98725000000002</v>
+        <v>320.52709428560047</v>
       </c>
       <c r="M31">
-        <v>0.21122536857445087</v>
+        <v>0.21125667433553613</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -8823,10 +8827,10 @@
         <v>297</v>
       </c>
       <c r="L32">
-        <v>487.83075000000002</v>
+        <v>334.60405375526341</v>
       </c>
       <c r="M32">
-        <v>0.20979805801036527</v>
+        <v>0.20976117170788547</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -8861,10 +8865,10 @@
         <v>297</v>
       </c>
       <c r="L33">
-        <v>361.87200000000001</v>
+        <v>269.01895782038702</v>
       </c>
       <c r="M33">
-        <v>0.20926427423559754</v>
+        <v>0.20928529799325452</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -8899,10 +8903,10 @@
         <v>297</v>
       </c>
       <c r="L34">
-        <v>469.81425000000002</v>
+        <v>322.60048966432225</v>
       </c>
       <c r="M34">
-        <v>0.20917291934046053</v>
+        <v>0.20903291449829686</v>
       </c>
       <c r="N34">
         <v>3</v>
@@ -8937,10 +8941,10 @@
         <v>297</v>
       </c>
       <c r="L35">
-        <v>368.58974999999998</v>
+        <v>265.38011071524255</v>
       </c>
       <c r="M35">
-        <v>0.20896477779603406</v>
+        <v>0.20891093849993769</v>
       </c>
       <c r="N35">
         <v>4</v>
@@ -8975,10 +8979,10 @@
         <v>297</v>
       </c>
       <c r="L36">
-        <v>342.52875</v>
+        <v>249.32336605345907</v>
       </c>
       <c r="M36">
-        <v>0.20238142107583679</v>
+        <v>0.20240387859406495</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -9013,10 +9017,10 @@
         <v>297</v>
       </c>
       <c r="L37">
-        <v>273.25349999999997</v>
+        <v>218.49019023835933</v>
       </c>
       <c r="M37">
-        <v>0.20150052289195122</v>
+        <v>0.20141742822170516</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -9051,10 +9055,10 @@
         <v>297</v>
       </c>
       <c r="L38">
-        <v>238.33199999999999</v>
+        <v>177.3863454156425</v>
       </c>
       <c r="M38">
-        <v>0.20056564631448578</v>
+        <v>0.20039080238529963</v>
       </c>
       <c r="N38">
         <v>3</v>
@@ -9089,10 +9093,10 @@
         <v>297</v>
       </c>
       <c r="L39">
-        <v>240.8955</v>
+        <v>175.61140442507488</v>
       </c>
       <c r="M39">
-        <v>0.1993283490341346</v>
+        <v>0.19924077548704913</v>
       </c>
       <c r="N39">
         <v>4</v>
@@ -9127,10 +9131,10 @@
         <v>297</v>
       </c>
       <c r="L40">
-        <v>183.45224999999999</v>
+        <v>130.95059677881818</v>
       </c>
       <c r="M40">
-        <v>0.19873374986430811</v>
+        <v>0.19876821706020437</v>
       </c>
       <c r="N40">
         <v>5</v>
@@ -9165,10 +9169,10 @@
         <v>297</v>
       </c>
       <c r="L41">
-        <v>71.643000000000001</v>
+        <v>61.317292061377806</v>
       </c>
       <c r="M41">
-        <v>0.19302622898511057</v>
+        <v>0.19304546410857523</v>
       </c>
       <c r="N41">
         <v>1</v>
@@ -9203,10 +9207,10 @@
         <v>297</v>
       </c>
       <c r="L42">
-        <v>84.502499999999998</v>
+        <v>73.91308836718062</v>
       </c>
       <c r="M42">
-        <v>0.19028913389088381</v>
+        <v>0.19010785296961721</v>
       </c>
       <c r="N42">
         <v>3</v>
@@ -9241,10 +9245,10 @@
         <v>297</v>
       </c>
       <c r="L43">
-        <v>89.121750000000006</v>
+        <v>73.833882572729578</v>
       </c>
       <c r="M43">
-        <v>0.18987656744152742</v>
+        <v>0.18975095986128188</v>
       </c>
       <c r="N43">
         <v>2</v>
@@ -9279,10 +9283,10 @@
         <v>297</v>
       </c>
       <c r="L44">
-        <v>78.735749999999996</v>
+        <v>71.556624018635546</v>
       </c>
       <c r="M44">
-        <v>0.1895409640536502</v>
+        <v>0.18931888596017796</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -9317,10 +9321,10 @@
         <v>297</v>
       </c>
       <c r="L45">
-        <v>38.14575</v>
+        <v>37.793592931990489</v>
       </c>
       <c r="M45">
-        <v>0.18785903852086452</v>
+        <v>0.18781755521414206</v>
       </c>
       <c r="N45">
         <v>5</v>
@@ -9355,10 +9359,10 @@
         <v>297</v>
       </c>
       <c r="L46">
-        <v>21.17475</v>
+        <v>20.943235857100667</v>
       </c>
       <c r="M46">
-        <v>0.18368356030668287</v>
+        <v>0.18367636760706385</v>
       </c>
       <c r="N46">
         <v>1</v>
@@ -9393,10 +9397,10 @@
         <v>297</v>
       </c>
       <c r="L47">
-        <v>12.65175</v>
+        <v>12.639451150730743</v>
       </c>
       <c r="M47">
-        <v>0.18209390376632326</v>
+        <v>0.18209662989041883</v>
       </c>
       <c r="N47">
         <v>3</v>
@@ -9431,10 +9435,10 @@
         <v>297</v>
       </c>
       <c r="L48">
-        <v>18.598500000000001</v>
+        <v>18.578628462053754</v>
       </c>
       <c r="M48">
-        <v>0.1807690179620571</v>
+        <v>0.18076747999102116</v>
       </c>
       <c r="N48">
         <v>2</v>
@@ -9469,10 +9473,10 @@
         <v>297</v>
       </c>
       <c r="L49">
-        <v>11.66175</v>
+        <v>11.622198434586581</v>
       </c>
       <c r="M49">
-        <v>0.18007030200367682</v>
+        <v>0.18007706514775951</v>
       </c>
       <c r="N49">
         <v>4</v>
@@ -9507,10 +9511,10 @@
         <v>297</v>
       </c>
       <c r="L50">
-        <v>0.43725000000000003</v>
+        <v>0.38409264125380005</v>
       </c>
       <c r="M50">
-        <v>0.17905926365446925</v>
+        <v>0.17850649984342556</v>
       </c>
       <c r="N50">
         <v>5</v>
@@ -9545,10 +9549,10 @@
         <v>297</v>
       </c>
       <c r="L51">
-        <v>1.4017500000000001</v>
+        <v>1.391932602782451</v>
       </c>
       <c r="M51">
-        <v>0.17112326507018999</v>
+        <v>0.1711232650701901</v>
       </c>
       <c r="N51">
         <v>2</v>
@@ -9583,7 +9587,7 @@
         <v>297</v>
       </c>
       <c r="L52">
-        <v>1.0605</v>
+        <v>1.0530256544678869</v>
       </c>
       <c r="M52">
         <v>0.1710889078794002</v>
@@ -9621,7 +9625,7 @@
         <v>297</v>
       </c>
       <c r="L53">
-        <v>0.06</v>
+        <v>5.8926893972340605E-2</v>
       </c>
       <c r="M53">
         <v>0.16991055299537561</v>
@@ -9659,7 +9663,7 @@
         <v>297</v>
       </c>
       <c r="L54">
-        <v>2.325E-2</v>
+        <v>1.4643391633609807E-2</v>
       </c>
       <c r="M54">
         <v>0.1687908114863759</v>
@@ -9697,7 +9701,7 @@
         <v>297</v>
       </c>
       <c r="L55">
-        <v>1.1655</v>
+        <v>1.1646867657208402</v>
       </c>
       <c r="M55">
         <v>0.1650043103908295</v>
@@ -9735,10 +9739,10 @@
         <v>297</v>
       </c>
       <c r="L56">
-        <v>6.0000000000000001E-3</v>
+        <v>3.9883009114406202E-3</v>
       </c>
       <c r="M56">
-        <v>0.1643242642718642</v>
+        <v>0.16432426427186431</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -9773,10 +9777,10 @@
         <v>297</v>
       </c>
       <c r="L57">
-        <v>8.9999999999999993E-3</v>
+        <v>6.5022770728315662E-3</v>
       </c>
       <c r="M57">
-        <v>0.16196123556854089</v>
+        <v>0.161961235568541</v>
       </c>
       <c r="N57">
         <v>3</v>
@@ -9887,7 +9891,7 @@
         <v>297</v>
       </c>
       <c r="L60">
-        <v>0.81599999999999995</v>
+        <v>0.77364403067522491</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -9925,13 +9929,13 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>5.2500000000000003E-3</v>
+        <v>3.2726001779475915</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -9963,13 +9967,13 @@
         <v>297</v>
       </c>
       <c r="L62">
-        <v>5.3414999999999999</v>
+        <v>4.4778378857750975E-2</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -10001,13 +10005,13 @@
         <v>297</v>
       </c>
       <c r="L63">
-        <v>4.5749999999999999E-2</v>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -10039,13 +10043,13 @@
         <v>297</v>
       </c>
       <c r="L64">
-        <v>3.2767499999999998</v>
+        <v>5.3282119260176248</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -10054,7 +10058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{148AA60F-8E4B-4143-B280-3CD903277654}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD131F0-1802-4537-848C-C6BD234EBE9B}">
   <dimension ref="B9:AB219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10175,10 +10179,10 @@
         <v>716</v>
       </c>
       <c r="L11">
-        <v>0.13275000000000001</v>
+        <v>7.3865363128491623E-2</v>
       </c>
       <c r="M11">
-        <v>0.64180968779611569</v>
+        <v>0.64180968609353928</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -10249,10 +10253,10 @@
         <v>716</v>
       </c>
       <c r="L12">
-        <v>1.35E-2</v>
+        <v>7.1862886505003141E-3</v>
       </c>
       <c r="M12">
-        <v>0.57270943763987581</v>
+        <v>0.57270943503833127</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -10323,10 +10327,10 @@
         <v>716</v>
       </c>
       <c r="L13">
-        <v>7.4999999999999997E-3</v>
+        <v>3.7874428837366726E-3</v>
       </c>
       <c r="M13">
-        <v>0.54215657633248249</v>
+        <v>0.54215657399093631</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -10397,10 +10401,10 @@
         <v>716</v>
       </c>
       <c r="L14">
-        <v>2.0430000000000001</v>
+        <v>1.2972876647387883</v>
       </c>
       <c r="M14">
-        <v>0.52755183382488857</v>
+        <v>0.52755183192501964</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -10436,7 +10440,7 @@
         <v>0.80025000000000002</v>
       </c>
       <c r="AA14">
-        <v>0.55530844395536094</v>
+        <v>0.55530844395536105</v>
       </c>
       <c r="AB14">
         <v>2</v>
@@ -10471,10 +10475,10 @@
         <v>716</v>
       </c>
       <c r="L15">
-        <v>0.20100000000000001</v>
+        <v>0.10089344680851063</v>
       </c>
       <c r="M15">
-        <v>0.51212117584922434</v>
+        <v>0.51212117278175018</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -10545,10 +10549,10 @@
         <v>716</v>
       </c>
       <c r="L16">
-        <v>0.85275000000000001</v>
+        <v>0.31582196159412623</v>
       </c>
       <c r="M16">
-        <v>0.41655078814050239</v>
+        <v>0.41655078677259522</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -10619,10 +10623,10 @@
         <v>716</v>
       </c>
       <c r="L17">
-        <v>2.8507500000000001</v>
+        <v>1.0908326349946442</v>
       </c>
       <c r="M17">
-        <v>0.41361153622829827</v>
+        <v>0.41361153397500883</v>
       </c>
       <c r="N17">
         <v>3</v>
@@ -10693,10 +10697,10 @@
         <v>716</v>
       </c>
       <c r="L18">
-        <v>1.494</v>
+        <v>0.61334966592427609</v>
       </c>
       <c r="M18">
-        <v>0.40830146275146834</v>
+        <v>0.40830146053218141</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -10767,10 +10771,10 @@
         <v>716</v>
       </c>
       <c r="L19">
-        <v>0.23474999999999999</v>
+        <v>9.4213507346981917E-2</v>
       </c>
       <c r="M19">
-        <v>0.40549123449547819</v>
+        <v>0.40549123234753132</v>
       </c>
       <c r="N19">
         <v>2</v>
@@ -10841,10 +10845,10 @@
         <v>716</v>
       </c>
       <c r="L20">
-        <v>0.15975</v>
+        <v>8.8289598231219887E-2</v>
       </c>
       <c r="M20">
-        <v>0.40198549254721339</v>
+        <v>0.4019854903809757</v>
       </c>
       <c r="N20">
         <v>2</v>
@@ -10880,7 +10884,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="AA20">
-        <v>0.4829318688683415</v>
+        <v>0.48293186886834161</v>
       </c>
       <c r="AB20">
         <v>1</v>
@@ -10915,10 +10919,10 @@
         <v>716</v>
       </c>
       <c r="L21">
-        <v>6.0000000000000001E-3</v>
+        <v>2.689637283299468E-3</v>
       </c>
       <c r="M21">
-        <v>0.39816191212636071</v>
+        <v>0.39816190937600981</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -10954,7 +10958,7 @@
         <v>0.41399999999999998</v>
       </c>
       <c r="AA21">
-        <v>0.46722753083539381</v>
+        <v>0.46722753083539392</v>
       </c>
       <c r="AB21">
         <v>1</v>
@@ -10989,10 +10993,10 @@
         <v>716</v>
       </c>
       <c r="L22">
-        <v>4.4999999999999997E-3</v>
+        <v>3.376665505529914E-3</v>
       </c>
       <c r="M22">
-        <v>0.39742800913107712</v>
+        <v>0.39772092516416935</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -11063,10 +11067,10 @@
         <v>716</v>
       </c>
       <c r="L23">
-        <v>8.4000000000000005E-2</v>
+        <v>3.3739170828010687E-2</v>
       </c>
       <c r="M23">
-        <v>0.39686119663669511</v>
+        <v>0.39686119416511878</v>
       </c>
       <c r="N23">
         <v>5</v>
@@ -11137,10 +11141,10 @@
         <v>716</v>
       </c>
       <c r="L24">
-        <v>0.12825</v>
+        <v>5.1924954152475764E-2</v>
       </c>
       <c r="M24">
-        <v>0.3967567309312956</v>
+        <v>0.39675672914896465</v>
       </c>
       <c r="N24">
         <v>3</v>
@@ -11211,10 +11215,10 @@
         <v>716</v>
       </c>
       <c r="L25">
-        <v>1.14825</v>
+        <v>0.46235715697904312</v>
       </c>
       <c r="M25">
-        <v>0.39375590014232559</v>
+        <v>0.39375589781587239</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -11285,10 +11289,10 @@
         <v>716</v>
       </c>
       <c r="L26">
-        <v>1.4624999999999999</v>
+        <v>0.49592172445088806</v>
       </c>
       <c r="M26">
-        <v>0.39061531417890655</v>
+        <v>0.39061531220285672</v>
       </c>
       <c r="N26">
         <v>2</v>
@@ -11359,10 +11363,10 @@
         <v>716</v>
       </c>
       <c r="L27">
-        <v>3.3750000000000002E-2</v>
+        <v>1.2118753040939737E-2</v>
       </c>
       <c r="M27">
-        <v>0.38669941709134431</v>
+        <v>0.38669941505144489</v>
       </c>
       <c r="N27">
         <v>3</v>
@@ -11433,10 +11437,10 @@
         <v>716</v>
       </c>
       <c r="L28">
-        <v>0.14174999999999999</v>
+        <v>4.9274817789175328E-2</v>
       </c>
       <c r="M28">
-        <v>0.3857251562281066</v>
+        <v>0.38572515452750761</v>
       </c>
       <c r="N28">
         <v>4</v>
@@ -11507,10 +11511,10 @@
         <v>716</v>
       </c>
       <c r="L29">
-        <v>0.111</v>
+        <v>5.0391535993219098E-2</v>
       </c>
       <c r="M29">
-        <v>0.38424647726408706</v>
+        <v>0.38424647487735197</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -11581,10 +11585,10 @@
         <v>716</v>
       </c>
       <c r="L30">
-        <v>6.3E-2</v>
+        <v>5.4672732362821948E-2</v>
       </c>
       <c r="M30">
-        <v>0.3816028221480296</v>
+        <v>0.38160282013561464</v>
       </c>
       <c r="N30">
         <v>5</v>
@@ -11655,10 +11659,10 @@
         <v>716</v>
       </c>
       <c r="L31">
-        <v>0.23474999999999999</v>
+        <v>0.16828302140815105</v>
       </c>
       <c r="M31">
-        <v>0.38144140337396321</v>
+        <v>0.38144140139662658</v>
       </c>
       <c r="N31">
         <v>3</v>
@@ -11729,10 +11733,10 @@
         <v>716</v>
       </c>
       <c r="L32">
-        <v>1.1579999999999999</v>
+        <v>0.54060127097930577</v>
       </c>
       <c r="M32">
-        <v>0.37771885770505959</v>
+        <v>0.37771885538388478</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -11803,10 +11807,10 @@
         <v>716</v>
       </c>
       <c r="L33">
-        <v>0.16125</v>
+        <v>8.298222744983913E-2</v>
       </c>
       <c r="M33">
-        <v>0.37580616105329778</v>
+        <v>0.37580615855679722</v>
       </c>
       <c r="N33">
         <v>4</v>
@@ -11842,7 +11846,7 @@
         <v>2.7524999999999999</v>
       </c>
       <c r="AA33">
-        <v>0.35518235628270461</v>
+        <v>0.35518235628270473</v>
       </c>
       <c r="AB33">
         <v>1</v>
@@ -11877,10 +11881,10 @@
         <v>716</v>
       </c>
       <c r="L34">
-        <v>1.9350000000000001</v>
+        <v>1.0997847708578143</v>
       </c>
       <c r="M34">
-        <v>0.36890812948880869</v>
+        <v>0.36890812756752811</v>
       </c>
       <c r="N34">
         <v>2</v>
@@ -11951,10 +11955,10 @@
         <v>716</v>
       </c>
       <c r="L35">
-        <v>3.2250000000000001E-2</v>
+        <v>2.9277042288295623E-2</v>
       </c>
       <c r="M35">
-        <v>0.36851610829010401</v>
+        <v>0.3685161057496793</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -12025,10 +12029,10 @@
         <v>716</v>
       </c>
       <c r="L36">
-        <v>0.87150000000000005</v>
+        <v>0.46790243194564746</v>
       </c>
       <c r="M36">
-        <v>0.36608033099901038</v>
+        <v>0.36608032809122826</v>
       </c>
       <c r="N36">
         <v>3</v>
@@ -12064,7 +12068,7 @@
         <v>1.5734999999999999</v>
       </c>
       <c r="AA36">
-        <v>0.34521107856007921</v>
+        <v>0.34521107856007932</v>
       </c>
       <c r="AB36">
         <v>3</v>
@@ -12099,10 +12103,10 @@
         <v>716</v>
       </c>
       <c r="L37">
-        <v>2.4682499999999998</v>
+        <v>1.1133897836304594</v>
       </c>
       <c r="M37">
-        <v>0.35873724915087268</v>
+        <v>0.35873504060189138</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -12138,7 +12142,7 @@
         <v>0.27300000000000002</v>
       </c>
       <c r="AA37">
-        <v>0.34175371912598163</v>
+        <v>0.34175371912598168</v>
       </c>
       <c r="AB37">
         <v>2</v>
@@ -12173,10 +12177,10 @@
         <v>716</v>
       </c>
       <c r="L38">
-        <v>0.84075</v>
+        <v>0.31956632723380701</v>
       </c>
       <c r="M38">
-        <v>0.357789384764092</v>
+        <v>0.35778098224498478</v>
       </c>
       <c r="N38">
         <v>3</v>
@@ -12212,7 +12216,7 @@
         <v>2.1487500000000002</v>
       </c>
       <c r="AA38">
-        <v>0.33769316778829123</v>
+        <v>0.33769316778829128</v>
       </c>
       <c r="AB38">
         <v>1</v>
@@ -12247,10 +12251,10 @@
         <v>716</v>
       </c>
       <c r="L39">
-        <v>0.11325</v>
+        <v>8.0012230596324202E-2</v>
       </c>
       <c r="M39">
-        <v>0.35777462392241838</v>
+        <v>0.3577746217438762</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -12321,10 +12325,10 @@
         <v>716</v>
       </c>
       <c r="L40">
-        <v>3.6367500000000001</v>
+        <v>1.530069773232563</v>
       </c>
       <c r="M40">
-        <v>0.35719254540175466</v>
+        <v>0.35720866019257785</v>
       </c>
       <c r="N40">
         <v>2</v>
@@ -12360,7 +12364,7 @@
         <v>11.225250000000001</v>
       </c>
       <c r="AA40">
-        <v>0.33113780911847024</v>
+        <v>0.33113780911847029</v>
       </c>
       <c r="AB40">
         <v>4</v>
@@ -12395,10 +12399,10 @@
         <v>716</v>
       </c>
       <c r="L41">
-        <v>0.93</v>
+        <v>0.35243719600969114</v>
       </c>
       <c r="M41">
-        <v>0.35627285284292481</v>
+        <v>0.35627681231345415</v>
       </c>
       <c r="N41">
         <v>4</v>
@@ -12434,7 +12438,7 @@
         <v>13.16025</v>
       </c>
       <c r="AA41">
-        <v>0.32839711167362323</v>
+        <v>0.3283971116736234</v>
       </c>
       <c r="AB41">
         <v>3</v>
@@ -12469,10 +12473,10 @@
         <v>716</v>
       </c>
       <c r="L42">
-        <v>9.3164999999999996</v>
+        <v>4.3111620099137307</v>
       </c>
       <c r="M42">
-        <v>0.35243606698786001</v>
+        <v>0.35243757698435063</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -12543,10 +12547,10 @@
         <v>716</v>
       </c>
       <c r="L43">
-        <v>3.819</v>
+        <v>1.5305312348534794</v>
       </c>
       <c r="M43">
-        <v>0.3516076617319962</v>
+        <v>0.35165596058353371</v>
       </c>
       <c r="N43">
         <v>2</v>
@@ -12582,7 +12586,7 @@
         <v>7.1617499999999996</v>
       </c>
       <c r="AA43">
-        <v>0.32792943662563495</v>
+        <v>0.32792943662563501</v>
       </c>
       <c r="AB43">
         <v>5</v>
@@ -12617,10 +12621,10 @@
         <v>716</v>
       </c>
       <c r="L44">
-        <v>0.29699999999999999</v>
+        <v>0.1245725615862316</v>
       </c>
       <c r="M44">
-        <v>0.34972108484019382</v>
+        <v>0.34972109205937246</v>
       </c>
       <c r="N44">
         <v>3</v>
@@ -12691,10 +12695,10 @@
         <v>716</v>
       </c>
       <c r="L45">
-        <v>1.335</v>
+        <v>0.61072475282802974</v>
       </c>
       <c r="M45">
-        <v>0.34770683807732244</v>
+        <v>0.34769065806150296</v>
       </c>
       <c r="N45">
         <v>4</v>
@@ -12730,7 +12734,7 @@
         <v>11.29275</v>
       </c>
       <c r="AA45">
-        <v>0.32284771703555426</v>
+        <v>0.32284771703555432</v>
       </c>
       <c r="AB45">
         <v>3</v>
@@ -12765,10 +12769,10 @@
         <v>716</v>
       </c>
       <c r="L46">
-        <v>1.55925</v>
+        <v>0.96415162721893488</v>
       </c>
       <c r="M46">
-        <v>0.34504038788484775</v>
+        <v>0.3450403855067361</v>
       </c>
       <c r="N46">
         <v>5</v>
@@ -12839,10 +12843,10 @@
         <v>716</v>
       </c>
       <c r="L47">
-        <v>1.0942499999999999</v>
+        <v>0.42928862834978837</v>
       </c>
       <c r="M47">
-        <v>0.34471412742159607</v>
+        <v>0.34471412495694309</v>
       </c>
       <c r="N47">
         <v>4</v>
@@ -12878,7 +12882,7 @@
         <v>9.6675000000000004</v>
       </c>
       <c r="AA47">
-        <v>0.32152841300460638</v>
+        <v>0.32152841300460649</v>
       </c>
       <c r="AB47">
         <v>4</v>
@@ -12913,10 +12917,10 @@
         <v>716</v>
       </c>
       <c r="L48">
-        <v>3.8137500000000002</v>
+        <v>1.7193153746365026</v>
       </c>
       <c r="M48">
-        <v>0.33834637316575383</v>
+        <v>0.338344008705949</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -12952,7 +12956,7 @@
         <v>17.933250000000001</v>
       </c>
       <c r="AA48">
-        <v>0.3210115290389895</v>
+        <v>0.32101152903898955</v>
       </c>
       <c r="AB48">
         <v>2</v>
@@ -12987,10 +12991,10 @@
         <v>716</v>
       </c>
       <c r="L49">
-        <v>2.4457499999999999</v>
+        <v>1.0155604327914562</v>
       </c>
       <c r="M49">
-        <v>0.33807097502071554</v>
+        <v>0.33807393060300145</v>
       </c>
       <c r="N49">
         <v>2</v>
@@ -13026,7 +13030,7 @@
         <v>9.5317500000000006</v>
       </c>
       <c r="AA49">
-        <v>0.31876403296109745</v>
+        <v>0.31876403296109757</v>
       </c>
       <c r="AB49">
         <v>5</v>
@@ -13061,10 +13065,10 @@
         <v>716</v>
       </c>
       <c r="L50">
-        <v>1.0365</v>
+        <v>0.38658870011853019</v>
       </c>
       <c r="M50">
-        <v>0.33783897090380921</v>
+        <v>0.3378389683679171</v>
       </c>
       <c r="N50">
         <v>5</v>
@@ -13135,10 +13139,10 @@
         <v>716</v>
       </c>
       <c r="L51">
-        <v>5.742</v>
+        <v>2.3971646903820814</v>
       </c>
       <c r="M51">
-        <v>0.33525113332665291</v>
+        <v>0.33525113069022772</v>
       </c>
       <c r="N51">
         <v>3</v>
@@ -13174,7 +13178,7 @@
         <v>10.093500000000001</v>
       </c>
       <c r="AA51">
-        <v>0.31069974805996092</v>
+        <v>0.31069974805996109</v>
       </c>
       <c r="AB51">
         <v>4</v>
@@ -13209,13 +13213,13 @@
         <v>716</v>
       </c>
       <c r="L52">
-        <v>2.0234999999999999</v>
+        <v>2.0674167214000665</v>
       </c>
       <c r="M52">
-        <v>0.33293825915646447</v>
+        <v>0.33287741793986247</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P52" t="s">
         <v>182</v>
@@ -13283,13 +13287,13 @@
         <v>716</v>
       </c>
       <c r="L53">
-        <v>4.7047499999999998</v>
+        <v>0.84868708482984845</v>
       </c>
       <c r="M53">
-        <v>0.33287416323073493</v>
+        <v>0.33270246610551035</v>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P53" t="s">
         <v>182</v>
@@ -13322,7 +13326,7 @@
         <v>7.08</v>
       </c>
       <c r="AA53">
-        <v>0.30718591643893717</v>
+        <v>0.30718591643893722</v>
       </c>
       <c r="AB53">
         <v>5</v>
@@ -13357,10 +13361,10 @@
         <v>716</v>
       </c>
       <c r="L54">
-        <v>2.0557500000000002</v>
+        <v>0.90688980672389197</v>
       </c>
       <c r="M54">
-        <v>0.33118897149672788</v>
+        <v>0.33065511729631791</v>
       </c>
       <c r="N54">
         <v>4</v>
@@ -13431,10 +13435,10 @@
         <v>716</v>
       </c>
       <c r="L55">
-        <v>5.1135000000000002</v>
+        <v>2.38156733624368</v>
       </c>
       <c r="M55">
-        <v>0.33003082124482852</v>
+        <v>0.33003117784307201</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -13505,10 +13509,10 @@
         <v>716</v>
       </c>
       <c r="L56">
-        <v>1.365</v>
+        <v>0.5786701359744838</v>
       </c>
       <c r="M56">
-        <v>0.3273154398620996</v>
+        <v>0.32731543839915989</v>
       </c>
       <c r="N56">
         <v>5</v>
@@ -13579,10 +13583,10 @@
         <v>716</v>
       </c>
       <c r="L57">
-        <v>4.851</v>
+        <v>2.2869846843177188</v>
       </c>
       <c r="M57">
-        <v>0.32267380490096631</v>
+        <v>0.3226738039144863</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -13653,10 +13657,10 @@
         <v>716</v>
       </c>
       <c r="L58">
-        <v>5.6085000000000003</v>
+        <v>2.445519657142857</v>
       </c>
       <c r="M58">
-        <v>0.31831214492557158</v>
+        <v>0.31831214301727478</v>
       </c>
       <c r="N58">
         <v>2</v>
@@ -13727,10 +13731,10 @@
         <v>716</v>
       </c>
       <c r="L59">
-        <v>5.742</v>
+        <v>2.1812305392950555</v>
       </c>
       <c r="M59">
-        <v>0.31551747722163281</v>
+        <v>0.315517475701454</v>
       </c>
       <c r="N59">
         <v>3</v>
@@ -13801,13 +13805,13 @@
         <v>716</v>
       </c>
       <c r="L60">
-        <v>3.0720000000000001</v>
+        <v>7.4466579404606295</v>
       </c>
       <c r="M60">
-        <v>0.31142168837471185</v>
+        <v>0.31144401312679909</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P60" t="s">
         <v>182</v>
@@ -13875,13 +13879,13 @@
         <v>716</v>
       </c>
       <c r="L61">
-        <v>15.60375</v>
+        <v>1.0526498150276995</v>
       </c>
       <c r="M61">
-        <v>0.31132934286767033</v>
+        <v>0.3114212009747484</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P61" t="s">
         <v>182</v>
@@ -13949,10 +13953,10 @@
         <v>716</v>
       </c>
       <c r="L62">
-        <v>6.0382499999999997</v>
+        <v>2.5053843596851979</v>
       </c>
       <c r="M62">
-        <v>0.31114352073899249</v>
+        <v>0.3111351472153539</v>
       </c>
       <c r="N62">
         <v>2</v>
@@ -13988,7 +13992,7 @@
         <v>7.5082500000000003</v>
       </c>
       <c r="AA62">
-        <v>0.29098582140379559</v>
+        <v>0.2909858214037957</v>
       </c>
       <c r="AB62">
         <v>2</v>
@@ -14023,10 +14027,10 @@
         <v>716</v>
       </c>
       <c r="L63">
-        <v>5.6812500000000004</v>
+        <v>2.2783537700661243</v>
       </c>
       <c r="M63">
-        <v>0.30895377068536056</v>
+        <v>0.30895377229938714</v>
       </c>
       <c r="N63">
         <v>4</v>
@@ -14062,7 +14066,7 @@
         <v>12.13575</v>
       </c>
       <c r="AA63">
-        <v>0.28804431370980027</v>
+        <v>0.28804431370980038</v>
       </c>
       <c r="AB63">
         <v>4</v>
@@ -14097,10 +14101,10 @@
         <v>716</v>
       </c>
       <c r="L64">
-        <v>8.4135000000000009</v>
+        <v>3.4400567625270559</v>
       </c>
       <c r="M64">
-        <v>0.30647219271038223</v>
+        <v>0.30647552218186846</v>
       </c>
       <c r="N64">
         <v>3</v>
@@ -14171,10 +14175,10 @@
         <v>716</v>
       </c>
       <c r="L65">
-        <v>15.31875</v>
+        <v>6.8329583287433868</v>
       </c>
       <c r="M65">
-        <v>0.30045362591603597</v>
+        <v>0.30046903711514461</v>
       </c>
       <c r="N65">
         <v>2</v>
@@ -14210,7 +14214,7 @@
         <v>8.9167500000000004</v>
       </c>
       <c r="AA65">
-        <v>0.28271473640787448</v>
+        <v>0.28271473640787459</v>
       </c>
       <c r="AB65">
         <v>3</v>
@@ -14245,10 +14249,10 @@
         <v>716</v>
       </c>
       <c r="L66">
-        <v>7.8360000000000003</v>
+        <v>3.0819163263223719</v>
       </c>
       <c r="M66">
-        <v>0.29925505455395174</v>
+        <v>0.29914480315155445</v>
       </c>
       <c r="N66">
         <v>5</v>
@@ -14319,10 +14323,10 @@
         <v>716</v>
       </c>
       <c r="L67">
-        <v>16.945499999999999</v>
+        <v>7.1139682354208436</v>
       </c>
       <c r="M67">
-        <v>0.29885035649752184</v>
+        <v>0.29886487728435684</v>
       </c>
       <c r="N67">
         <v>3</v>
@@ -14358,7 +14362,7 @@
         <v>17.138999999999999</v>
       </c>
       <c r="AA67">
-        <v>0.27884040587498132</v>
+        <v>0.27884040587498138</v>
       </c>
       <c r="AB67">
         <v>1</v>
@@ -14393,10 +14397,10 @@
         <v>716</v>
       </c>
       <c r="L68">
-        <v>15.122249999999999</v>
+        <v>5.6821607014118145</v>
       </c>
       <c r="M68">
-        <v>0.29869248634671575</v>
+        <v>0.2986591158476577</v>
       </c>
       <c r="N68">
         <v>4</v>
@@ -14432,7 +14436,7 @@
         <v>11.24175</v>
       </c>
       <c r="AA68">
-        <v>0.27849146326729413</v>
+        <v>0.27849146326729418</v>
       </c>
       <c r="AB68">
         <v>2</v>
@@ -14467,10 +14471,10 @@
         <v>716</v>
       </c>
       <c r="L69">
-        <v>22.609500000000001</v>
+        <v>10.63323450116059</v>
       </c>
       <c r="M69">
-        <v>0.2982235493365864</v>
+        <v>0.29827699882944375</v>
       </c>
       <c r="N69">
         <v>1</v>
@@ -14506,7 +14510,7 @@
         <v>5.8087499999999999</v>
       </c>
       <c r="AA69">
-        <v>0.27765995522612563</v>
+        <v>0.27765995522612574</v>
       </c>
       <c r="AB69">
         <v>5</v>
@@ -14541,10 +14545,10 @@
         <v>716</v>
       </c>
       <c r="L70">
-        <v>28.51275</v>
+        <v>13.113737247985041</v>
       </c>
       <c r="M70">
-        <v>0.29228905840273373</v>
+        <v>0.29229093216599061</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -14580,7 +14584,7 @@
         <v>7.6492500000000003</v>
       </c>
       <c r="AA70">
-        <v>0.27151627717550131</v>
+        <v>0.27151627717550136</v>
       </c>
       <c r="AB70">
         <v>1</v>
@@ -14615,10 +14619,10 @@
         <v>716</v>
       </c>
       <c r="L71">
-        <v>22.640999999999998</v>
+        <v>7.6680980057411494</v>
       </c>
       <c r="M71">
-        <v>0.29061795841895516</v>
+        <v>0.29074998547532971</v>
       </c>
       <c r="N71">
         <v>4</v>
@@ -14654,7 +14658,7 @@
         <v>7.1295000000000002</v>
       </c>
       <c r="AA71">
-        <v>0.27128003522570476</v>
+        <v>0.27128003522570482</v>
       </c>
       <c r="AB71">
         <v>5</v>
@@ -14689,10 +14693,10 @@
         <v>716</v>
       </c>
       <c r="L72">
-        <v>11.358000000000001</v>
+        <v>3.4832850777390085</v>
       </c>
       <c r="M72">
-        <v>0.29012257495856547</v>
+        <v>0.29012401575277419</v>
       </c>
       <c r="N72">
         <v>5</v>
@@ -14763,10 +14767,10 @@
         <v>716</v>
       </c>
       <c r="L73">
-        <v>22.345500000000001</v>
+        <v>8.1910663833340873</v>
       </c>
       <c r="M73">
-        <v>0.28936638016656602</v>
+        <v>0.28936186932816366</v>
       </c>
       <c r="N73">
         <v>3</v>
@@ -14837,10 +14841,10 @@
         <v>716</v>
       </c>
       <c r="L74">
-        <v>17.9175</v>
+        <v>8.1867454379726574</v>
       </c>
       <c r="M74">
-        <v>0.28857626490011229</v>
+        <v>0.28868109212333803</v>
       </c>
       <c r="N74">
         <v>2</v>
@@ -14876,7 +14880,7 @@
         <v>5.9865000000000004</v>
       </c>
       <c r="AA74">
-        <v>0.26606689708566378</v>
+        <v>0.26606689708566383</v>
       </c>
       <c r="AB74">
         <v>3</v>
@@ -14911,10 +14915,10 @@
         <v>716</v>
       </c>
       <c r="L75">
-        <v>24.6555</v>
+        <v>9.9790166147362793</v>
       </c>
       <c r="M75">
-        <v>0.28139935019120027</v>
+        <v>0.28142831322454376</v>
       </c>
       <c r="N75">
         <v>3</v>
@@ -14985,10 +14989,10 @@
         <v>716</v>
       </c>
       <c r="L76">
-        <v>32.369999999999997</v>
+        <v>13.700402799451847</v>
       </c>
       <c r="M76">
-        <v>0.28072322303107566</v>
+        <v>0.28066882553775885</v>
       </c>
       <c r="N76">
         <v>2</v>
@@ -15059,10 +15063,10 @@
         <v>716</v>
       </c>
       <c r="L77">
-        <v>24.038250000000001</v>
+        <v>8.1417755876443643</v>
       </c>
       <c r="M77">
-        <v>0.2792811805848488</v>
+        <v>0.27933114333386205</v>
       </c>
       <c r="N77">
         <v>4</v>
@@ -15133,10 +15137,10 @@
         <v>716</v>
       </c>
       <c r="L78">
-        <v>13.776</v>
+        <v>4.6822461400917641</v>
       </c>
       <c r="M78">
-        <v>0.27911153649445308</v>
+        <v>0.27876711596728176</v>
       </c>
       <c r="N78">
         <v>5</v>
@@ -15172,7 +15176,7 @@
         <v>9.282</v>
       </c>
       <c r="AA78">
-        <v>0.25903571450424367</v>
+        <v>0.25903571450424379</v>
       </c>
       <c r="AB78">
         <v>1</v>
@@ -15207,10 +15211,10 @@
         <v>716</v>
       </c>
       <c r="L79">
-        <v>34.360500000000002</v>
+        <v>15.487709365156677</v>
       </c>
       <c r="M79">
-        <v>0.27859271590165946</v>
+        <v>0.27863956281191982</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -15281,13 +15285,13 @@
         <v>716</v>
       </c>
       <c r="L80">
-        <v>24.252749999999999</v>
+        <v>11.353581518274941</v>
       </c>
       <c r="M80">
-        <v>0.27002815741850811</v>
+        <v>0.27022090326173365</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P80" t="s">
         <v>182</v>
@@ -15355,13 +15359,13 @@
         <v>716</v>
       </c>
       <c r="L81">
-        <v>23.854500000000002</v>
+        <v>7.9827790709137814</v>
       </c>
       <c r="M81">
-        <v>0.27000188439396738</v>
+        <v>0.27005185848429036</v>
       </c>
       <c r="N81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P81" t="s">
         <v>182</v>
@@ -15429,10 +15433,10 @@
         <v>716</v>
       </c>
       <c r="L82">
-        <v>28.257000000000001</v>
+        <v>12.246641285361399</v>
       </c>
       <c r="M82">
-        <v>0.26954962710095742</v>
+        <v>0.26972473894364579</v>
       </c>
       <c r="N82">
         <v>2</v>
@@ -15503,10 +15507,10 @@
         <v>716</v>
       </c>
       <c r="L83">
-        <v>19.673999999999999</v>
+        <v>7.3108464738887342</v>
       </c>
       <c r="M83">
-        <v>0.26939596618201267</v>
+        <v>0.26955856564957159</v>
       </c>
       <c r="N83">
         <v>3</v>
@@ -15542,7 +15546,7 @@
         <v>13.77</v>
       </c>
       <c r="AA83">
-        <v>0.24933276071846933</v>
+        <v>0.24933276071846938</v>
       </c>
       <c r="AB83">
         <v>2</v>
@@ -15577,10 +15581,10 @@
         <v>716</v>
       </c>
       <c r="L84">
-        <v>11.29425</v>
+        <v>3.3490710683504861</v>
       </c>
       <c r="M84">
-        <v>0.26704885959550245</v>
+        <v>0.26706070599589044</v>
       </c>
       <c r="N84">
         <v>5</v>
@@ -15651,10 +15655,10 @@
         <v>716</v>
       </c>
       <c r="L85">
-        <v>8.4990000000000006</v>
+        <v>2.7518448619544609</v>
       </c>
       <c r="M85">
-        <v>0.26383215404968025</v>
+        <v>0.26371909563033769</v>
       </c>
       <c r="N85">
         <v>5</v>
@@ -15690,7 +15694,7 @@
         <v>12.5565</v>
       </c>
       <c r="AA85">
-        <v>0.24238823606002166</v>
+        <v>0.24238823606002172</v>
       </c>
       <c r="AB85">
         <v>3</v>
@@ -15725,10 +15729,10 @@
         <v>716</v>
       </c>
       <c r="L86">
-        <v>28.513500000000001</v>
+        <v>9.4451467060414434</v>
       </c>
       <c r="M86">
-        <v>0.2617794637762782</v>
+        <v>0.2617705238247936</v>
       </c>
       <c r="N86">
         <v>4</v>
@@ -15764,7 +15768,7 @@
         <v>11.795999999999999</v>
       </c>
       <c r="AA86">
-        <v>0.24096404328716831</v>
+        <v>0.24096404328716839</v>
       </c>
       <c r="AB86">
         <v>4</v>
@@ -15799,10 +15803,10 @@
         <v>716</v>
       </c>
       <c r="L87">
-        <v>34.002000000000002</v>
+        <v>14.738328126264811</v>
       </c>
       <c r="M87">
-        <v>0.26003924764684239</v>
+        <v>0.25997229098577529</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -15838,7 +15842,7 @@
         <v>6.3847500000000004</v>
       </c>
       <c r="AA87">
-        <v>0.23863714544768214</v>
+        <v>0.23863714544768222</v>
       </c>
       <c r="AB87">
         <v>1</v>
@@ -15873,10 +15877,10 @@
         <v>716</v>
       </c>
       <c r="L88">
-        <v>30.776250000000001</v>
+        <v>12.536336496250751</v>
       </c>
       <c r="M88">
-        <v>0.25921216680767006</v>
+        <v>0.25921461779183075</v>
       </c>
       <c r="N88">
         <v>2</v>
@@ -15912,7 +15916,7 @@
         <v>0.33524999999999999</v>
       </c>
       <c r="AA88">
-        <v>0.23846908990471902</v>
+        <v>0.23846908990471913</v>
       </c>
       <c r="AB88">
         <v>5</v>
@@ -15947,10 +15951,10 @@
         <v>716</v>
       </c>
       <c r="L89">
-        <v>24.00375</v>
+        <v>9.127649260124608</v>
       </c>
       <c r="M89">
-        <v>0.25881666986173618</v>
+        <v>0.2587796525585197</v>
       </c>
       <c r="N89">
         <v>3</v>
@@ -16021,10 +16025,10 @@
         <v>716</v>
       </c>
       <c r="L90">
-        <v>24.306000000000001</v>
+        <v>10.060963313383887</v>
       </c>
       <c r="M90">
-        <v>0.25260122628882653</v>
+        <v>0.2525998536350848</v>
       </c>
       <c r="N90">
         <v>2</v>
@@ -16060,7 +16064,7 @@
         <v>3.4304999999999999</v>
       </c>
       <c r="AA90">
-        <v>0.23408944744576379</v>
+        <v>0.2340894474457639</v>
       </c>
       <c r="AB90">
         <v>3</v>
@@ -16095,10 +16099,10 @@
         <v>716</v>
       </c>
       <c r="L91">
-        <v>25.912500000000001</v>
+        <v>8.9368476007866331</v>
       </c>
       <c r="M91">
-        <v>0.25153417899496011</v>
+        <v>0.25150733601446446</v>
       </c>
       <c r="N91">
         <v>3</v>
@@ -16169,10 +16173,10 @@
         <v>716</v>
       </c>
       <c r="L92">
-        <v>20.394749999999998</v>
+        <v>8.8128603457248591</v>
       </c>
       <c r="M92">
-        <v>0.25060338783149372</v>
+        <v>0.25071167267785949</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -16208,7 +16212,7 @@
         <v>2.4982500000000001</v>
       </c>
       <c r="AA92">
-        <v>0.22991689876912511</v>
+        <v>0.22991689876912519</v>
       </c>
       <c r="AB92">
         <v>1</v>
@@ -16243,10 +16247,10 @@
         <v>716</v>
       </c>
       <c r="L93">
-        <v>22.77225</v>
+        <v>7.2329978699142732</v>
       </c>
       <c r="M93">
-        <v>0.25013574851877562</v>
+        <v>0.25012816856488962</v>
       </c>
       <c r="N93">
         <v>4</v>
@@ -16317,10 +16321,10 @@
         <v>716</v>
       </c>
       <c r="L94">
-        <v>7.4325000000000001</v>
+        <v>2.2870648114190533</v>
       </c>
       <c r="M94">
-        <v>0.24813053223666148</v>
+        <v>0.24842085354908597</v>
       </c>
       <c r="N94">
         <v>5</v>
@@ -16391,10 +16395,10 @@
         <v>716</v>
       </c>
       <c r="L95">
-        <v>12.948</v>
+        <v>3.8996706500377822</v>
       </c>
       <c r="M95">
-        <v>0.2424731013582532</v>
+        <v>0.24248897477406714</v>
       </c>
       <c r="N95">
         <v>5</v>
@@ -16465,10 +16469,10 @@
         <v>716</v>
       </c>
       <c r="L96">
-        <v>28.251750000000001</v>
+        <v>9.3518493058088143</v>
       </c>
       <c r="M96">
-        <v>0.24170697386623632</v>
+        <v>0.24168145276502528</v>
       </c>
       <c r="N96">
         <v>4</v>
@@ -16539,10 +16543,10 @@
         <v>716</v>
       </c>
       <c r="L97">
-        <v>28.21725</v>
+        <v>11.139077899514813</v>
       </c>
       <c r="M97">
-        <v>0.23868400043605867</v>
+        <v>0.23844854884769676</v>
       </c>
       <c r="N97">
         <v>3</v>
@@ -16578,7 +16582,7 @@
         <v>1.9117500000000001</v>
       </c>
       <c r="AA97">
-        <v>0.2167624556695007</v>
+        <v>0.21676245566950081</v>
       </c>
       <c r="AB97">
         <v>2</v>
@@ -16613,10 +16617,10 @@
         <v>716</v>
       </c>
       <c r="L98">
-        <v>32.496000000000002</v>
+        <v>12.840128269530574</v>
       </c>
       <c r="M98">
-        <v>0.23835190239123727</v>
+        <v>0.23838200587307795</v>
       </c>
       <c r="N98">
         <v>2</v>
@@ -16687,10 +16691,10 @@
         <v>716</v>
       </c>
       <c r="L99">
-        <v>31.69875</v>
+        <v>13.440503789044175</v>
       </c>
       <c r="M99">
-        <v>0.23767013747240986</v>
+        <v>0.23758628183242297</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -16726,7 +16730,7 @@
         <v>5.4240000000000004</v>
       </c>
       <c r="AA99">
-        <v>0.21490191909175357</v>
+        <v>0.21490191909175371</v>
       </c>
       <c r="AB99">
         <v>3</v>
@@ -16761,10 +16765,10 @@
         <v>716</v>
       </c>
       <c r="L100">
-        <v>9.0487500000000001</v>
+        <v>2.6237974555633863</v>
       </c>
       <c r="M100">
-        <v>0.23321291436204147</v>
+        <v>0.23311381661374375</v>
       </c>
       <c r="N100">
         <v>5</v>
@@ -16835,10 +16839,10 @@
         <v>716</v>
       </c>
       <c r="L101">
-        <v>33.929250000000003</v>
+        <v>10.875266526816789</v>
       </c>
       <c r="M101">
-        <v>0.23193956389415799</v>
+        <v>0.23190993556351075</v>
       </c>
       <c r="N101">
         <v>4</v>
@@ -16909,10 +16913,10 @@
         <v>716</v>
       </c>
       <c r="L102">
-        <v>33.958500000000001</v>
+        <v>14.854431034605263</v>
       </c>
       <c r="M102">
-        <v>0.23036434092668812</v>
+        <v>0.23038554243211543</v>
       </c>
       <c r="N102">
         <v>2</v>
@@ -16983,10 +16987,10 @@
         <v>716</v>
       </c>
       <c r="L103">
-        <v>28.570499999999999</v>
+        <v>10.995952661349133</v>
       </c>
       <c r="M103">
-        <v>0.22921900967611925</v>
+        <v>0.22923250667296893</v>
       </c>
       <c r="N103">
         <v>3</v>
@@ -17057,10 +17061,10 @@
         <v>716</v>
       </c>
       <c r="L104">
-        <v>33.893999999999998</v>
+        <v>16.022853028024706</v>
       </c>
       <c r="M104">
-        <v>0.22838075718487735</v>
+        <v>0.22830047432693074</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -17131,10 +17135,10 @@
         <v>716</v>
       </c>
       <c r="L105">
-        <v>18.38775</v>
+        <v>6.2410580780377201</v>
       </c>
       <c r="M105">
-        <v>0.22094673084234145</v>
+        <v>0.22099777727611139</v>
       </c>
       <c r="N105">
         <v>4</v>
@@ -17205,10 +17209,10 @@
         <v>716</v>
       </c>
       <c r="L106">
-        <v>23.91825</v>
+        <v>9.1447419198326081</v>
       </c>
       <c r="M106">
-        <v>0.22009479693180239</v>
+        <v>0.22007702497540099</v>
       </c>
       <c r="N106">
         <v>2</v>
@@ -17244,7 +17248,7 @@
         <v>0.96750000000000003</v>
       </c>
       <c r="AA106">
-        <v>0.19718537994660379</v>
+        <v>0.1971853799466039</v>
       </c>
       <c r="AB106">
         <v>1</v>
@@ -17279,10 +17283,10 @@
         <v>716</v>
       </c>
       <c r="L107">
-        <v>26.395499999999998</v>
+        <v>10.469037839998537</v>
       </c>
       <c r="M107">
-        <v>0.21918009901496999</v>
+        <v>0.2190923675874179</v>
       </c>
       <c r="N107">
         <v>3</v>
@@ -17353,10 +17357,10 @@
         <v>716</v>
       </c>
       <c r="L108">
-        <v>22.7715</v>
+        <v>6.9885791726529458</v>
       </c>
       <c r="M108">
-        <v>0.21900888057438397</v>
+        <v>0.21906828414362833</v>
       </c>
       <c r="N108">
         <v>5</v>
@@ -17427,10 +17431,10 @@
         <v>716</v>
       </c>
       <c r="L109">
-        <v>28.026</v>
+        <v>13.478514288348036</v>
       </c>
       <c r="M109">
-        <v>0.21863866869951187</v>
+        <v>0.21870025487918579</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -17466,7 +17470,7 @@
         <v>4.2127499999999998</v>
       </c>
       <c r="AA109">
-        <v>0.19155540310057456</v>
+        <v>0.19155540310057462</v>
       </c>
       <c r="AB109">
         <v>3</v>
@@ -17501,10 +17505,10 @@
         <v>716</v>
       </c>
       <c r="L110">
-        <v>39.694499999999998</v>
+        <v>16.880692577416887</v>
       </c>
       <c r="M110">
-        <v>0.21067703776151411</v>
+        <v>0.21066806190548948</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -17540,7 +17544,7 @@
         <v>0.66449999999999998</v>
       </c>
       <c r="AA110">
-        <v>0.18993154813753857</v>
+        <v>0.18993154813753862</v>
       </c>
       <c r="AB110">
         <v>2</v>
@@ -17575,10 +17579,10 @@
         <v>716</v>
       </c>
       <c r="L111">
-        <v>33.929250000000003</v>
+        <v>11.536771012603353</v>
       </c>
       <c r="M111">
-        <v>0.21036921847458401</v>
+        <v>0.21039603809370558</v>
       </c>
       <c r="N111">
         <v>4</v>
@@ -17649,10 +17653,10 @@
         <v>716</v>
       </c>
       <c r="L112">
-        <v>25.317</v>
+        <v>7.9394035074743643</v>
       </c>
       <c r="M112">
-        <v>0.20986841286404934</v>
+        <v>0.21005896648512856</v>
       </c>
       <c r="N112">
         <v>5</v>
@@ -17723,10 +17727,10 @@
         <v>716</v>
       </c>
       <c r="L113">
-        <v>33.684750000000001</v>
+        <v>14.458925368233729</v>
       </c>
       <c r="M113">
-        <v>0.20976464124929756</v>
+        <v>0.20960154767938133</v>
       </c>
       <c r="N113">
         <v>2</v>
@@ -17797,10 +17801,10 @@
         <v>716</v>
       </c>
       <c r="L114">
-        <v>34.176749999999998</v>
+        <v>12.93501317651134</v>
       </c>
       <c r="M114">
-        <v>0.20929861291636676</v>
+        <v>0.20934272472412338</v>
       </c>
       <c r="N114">
         <v>3</v>
@@ -17871,10 +17875,10 @@
         <v>716</v>
       </c>
       <c r="L115">
-        <v>39.153750000000002</v>
+        <v>16.826841866494039</v>
       </c>
       <c r="M115">
-        <v>0.20076514591256939</v>
+        <v>0.20066469663821215</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -17945,10 +17949,10 @@
         <v>716</v>
       </c>
       <c r="L116">
-        <v>37.652250000000002</v>
+        <v>13.458140942157598</v>
       </c>
       <c r="M116">
-        <v>0.20005246426473414</v>
+        <v>0.19996156199907517</v>
       </c>
       <c r="N116">
         <v>4</v>
@@ -18019,10 +18023,10 @@
         <v>716</v>
       </c>
       <c r="L117">
-        <v>36.28125</v>
+        <v>14.732523528929709</v>
       </c>
       <c r="M117">
-        <v>0.19950335975762765</v>
+        <v>0.19926293087445288</v>
       </c>
       <c r="N117">
         <v>3</v>
@@ -18058,7 +18062,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="AA117">
-        <v>0.1682606965362245</v>
+        <v>0.16826069653622461</v>
       </c>
       <c r="AB117">
         <v>1</v>
@@ -18093,10 +18097,10 @@
         <v>716</v>
       </c>
       <c r="L118">
-        <v>39.276000000000003</v>
+        <v>16.11558376924847</v>
       </c>
       <c r="M118">
-        <v>0.19803043136473986</v>
+        <v>0.19841164512962051</v>
       </c>
       <c r="N118">
         <v>2</v>
@@ -18167,10 +18171,10 @@
         <v>716</v>
       </c>
       <c r="L119">
-        <v>33.84375</v>
+        <v>10.752138120229295</v>
       </c>
       <c r="M119">
-        <v>0.19742869010670552</v>
+        <v>0.19761805014211203</v>
       </c>
       <c r="N119">
         <v>5</v>
@@ -18206,7 +18210,7 @@
         <v>3.8249999999999999E-2</v>
       </c>
       <c r="AA119">
-        <v>0.16184926500859079</v>
+        <v>0.1618492650085909</v>
       </c>
       <c r="AB119">
         <v>3</v>
@@ -18241,10 +18245,10 @@
         <v>716</v>
       </c>
       <c r="L120">
-        <v>55.926000000000002</v>
+        <v>23.389625919863505</v>
       </c>
       <c r="M120">
-        <v>0.18996312557922815</v>
+        <v>0.18989220297382184</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -18315,10 +18319,10 @@
         <v>716</v>
       </c>
       <c r="L121">
-        <v>54.885750000000002</v>
+        <v>19.178416321103857</v>
       </c>
       <c r="M121">
-        <v>0.18952984304316484</v>
+        <v>0.1895775749818904</v>
       </c>
       <c r="N121">
         <v>4</v>
@@ -18389,10 +18393,10 @@
         <v>716</v>
       </c>
       <c r="L122">
-        <v>56.678249999999998</v>
+        <v>21.897278361085565</v>
       </c>
       <c r="M122">
-        <v>0.18923620032405356</v>
+        <v>0.18950176936541294</v>
       </c>
       <c r="N122">
         <v>3</v>
@@ -18428,7 +18432,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="AA122">
-        <v>0.15540649959545319</v>
+        <v>0.1554064995954533</v>
       </c>
       <c r="AB122">
         <v>2</v>
@@ -18463,10 +18467,10 @@
         <v>716</v>
       </c>
       <c r="L123">
-        <v>56.515500000000003</v>
+        <v>23.269612438856104</v>
       </c>
       <c r="M123">
-        <v>0.18902698769039974</v>
+        <v>0.18903655079551923</v>
       </c>
       <c r="N123">
         <v>2</v>
@@ -18537,10 +18541,10 @@
         <v>716</v>
       </c>
       <c r="L124">
-        <v>45.358499999999999</v>
+        <v>13.743739207359916</v>
       </c>
       <c r="M124">
-        <v>0.18832676528282405</v>
+        <v>0.18821123030359993</v>
       </c>
       <c r="N124">
         <v>5</v>
@@ -18611,10 +18615,10 @@
         <v>716</v>
       </c>
       <c r="L125">
-        <v>55.462499999999999</v>
+        <v>20.643554236437982</v>
       </c>
       <c r="M125">
-        <v>0.18106169458735505</v>
+        <v>0.18098766426815993</v>
       </c>
       <c r="N125">
         <v>2</v>
@@ -18685,10 +18689,10 @@
         <v>716</v>
       </c>
       <c r="L126">
-        <v>56.410499999999999</v>
+        <v>20.358929758111969</v>
       </c>
       <c r="M126">
-        <v>0.18008115423650342</v>
+        <v>0.18006720524599179</v>
       </c>
       <c r="N126">
         <v>4</v>
@@ -18759,10 +18763,10 @@
         <v>716</v>
       </c>
       <c r="L127">
-        <v>55.648499999999999</v>
+        <v>21.353211098434027</v>
       </c>
       <c r="M127">
-        <v>0.17982167713659736</v>
+        <v>0.17981694211412488</v>
       </c>
       <c r="N127">
         <v>3</v>
@@ -18833,10 +18837,10 @@
         <v>716</v>
       </c>
       <c r="L128">
-        <v>55.621499999999997</v>
+        <v>25.59641229854369</v>
       </c>
       <c r="M128">
-        <v>0.17979833796450664</v>
+        <v>0.17960788650668466</v>
       </c>
       <c r="N128">
         <v>1</v>
@@ -18872,7 +18876,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="AA128">
-        <v>0.1235548106226302</v>
+        <v>0.1235548106226303</v>
       </c>
       <c r="AB128">
         <v>3</v>
@@ -18907,10 +18911,10 @@
         <v>716</v>
       </c>
       <c r="L129">
-        <v>57.026249999999997</v>
+        <v>17.004811917923984</v>
       </c>
       <c r="M129">
-        <v>0.17811234429218911</v>
+        <v>0.17811465402695262</v>
       </c>
       <c r="N129">
         <v>5</v>
@@ -18981,10 +18985,10 @@
         <v>716</v>
       </c>
       <c r="L130">
-        <v>56.383499999999998</v>
+        <v>19.642701642140754</v>
       </c>
       <c r="M130">
-        <v>0.1704319463307053</v>
+        <v>0.17038531443652866</v>
       </c>
       <c r="N130">
         <v>3</v>
@@ -19055,10 +19059,10 @@
         <v>716</v>
       </c>
       <c r="L131">
-        <v>55.984499999999997</v>
+        <v>20.220373742702396</v>
       </c>
       <c r="M131">
-        <v>0.17006010619444101</v>
+        <v>0.17006613251376379</v>
       </c>
       <c r="N131">
         <v>2</v>
@@ -19129,10 +19133,10 @@
         <v>716</v>
       </c>
       <c r="L132">
-        <v>56.606999999999999</v>
+        <v>18.497898678850266</v>
       </c>
       <c r="M132">
-        <v>0.1693977660912247</v>
+        <v>0.16938116921238872</v>
       </c>
       <c r="N132">
         <v>4</v>
@@ -19203,10 +19207,10 @@
         <v>716</v>
       </c>
       <c r="L133">
-        <v>52.285499999999999</v>
+        <v>15.598994012147754</v>
       </c>
       <c r="M133">
-        <v>0.16917766588378633</v>
+        <v>0.16921737264405656</v>
       </c>
       <c r="N133">
         <v>5</v>
@@ -19241,10 +19245,10 @@
         <v>716</v>
       </c>
       <c r="L134">
-        <v>62.124000000000002</v>
+        <v>26.119589805985147</v>
       </c>
       <c r="M134">
-        <v>0.16889404764958146</v>
+        <v>0.1687893703877805</v>
       </c>
       <c r="N134">
         <v>1</v>
@@ -19279,13 +19283,13 @@
         <v>716</v>
       </c>
       <c r="L135">
-        <v>75.061499999999995</v>
+        <v>26.770762808132368</v>
       </c>
       <c r="M135">
-        <v>0.16063150870942555</v>
+        <v>0.16063540836771856</v>
       </c>
       <c r="N135">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="2:28">
@@ -19317,13 +19321,13 @@
         <v>716</v>
       </c>
       <c r="L136">
-        <v>78.972750000000005</v>
+        <v>23.843669406039179</v>
       </c>
       <c r="M136">
-        <v>0.16060024717445442</v>
+        <v>0.16062250507718498</v>
       </c>
       <c r="N136">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="2:28">
@@ -19355,10 +19359,10 @@
         <v>716</v>
       </c>
       <c r="L137">
-        <v>79.352999999999994</v>
+        <v>29.218031137858727</v>
       </c>
       <c r="M137">
-        <v>0.16032505166361663</v>
+        <v>0.16049668618562413</v>
       </c>
       <c r="N137">
         <v>2</v>
@@ -19393,10 +19397,10 @@
         <v>716</v>
       </c>
       <c r="L138">
-        <v>76.126499999999993</v>
+        <v>32.539826044330987</v>
       </c>
       <c r="M138">
-        <v>0.15935574878055114</v>
+        <v>0.15911295918523696</v>
       </c>
       <c r="N138">
         <v>1</v>
@@ -19431,10 +19435,10 @@
         <v>716</v>
       </c>
       <c r="L139">
-        <v>69.805499999999995</v>
+        <v>20.628587147827812</v>
       </c>
       <c r="M139">
-        <v>0.15865393585494086</v>
+        <v>0.15871660207254587</v>
       </c>
       <c r="N139">
         <v>5</v>
@@ -19469,10 +19473,10 @@
         <v>716</v>
       </c>
       <c r="L140">
-        <v>78.054000000000002</v>
+        <v>36.265682124372354</v>
       </c>
       <c r="M140">
-        <v>0.1505820492347977</v>
+        <v>0.15061346938734776</v>
       </c>
       <c r="N140">
         <v>1</v>
@@ -19507,13 +19511,13 @@
         <v>716</v>
       </c>
       <c r="L141">
-        <v>69.370500000000007</v>
+        <v>20.8490448455935</v>
       </c>
       <c r="M141">
-        <v>0.15022469416350986</v>
+        <v>0.15025145444745847</v>
       </c>
       <c r="N141">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="2:28">
@@ -19545,13 +19549,13 @@
         <v>716</v>
       </c>
       <c r="L142">
-        <v>67.293000000000006</v>
+        <v>23.759262736187782</v>
       </c>
       <c r="M142">
-        <v>0.15002513809285734</v>
+        <v>0.14999962364772257</v>
       </c>
       <c r="N142">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="2:28">
@@ -19583,10 +19587,10 @@
         <v>716</v>
       </c>
       <c r="L143">
-        <v>73.551749999999998</v>
+        <v>24.655698070390287</v>
       </c>
       <c r="M143">
-        <v>0.14917254774391039</v>
+        <v>0.14908538711334962</v>
       </c>
       <c r="N143">
         <v>2</v>
@@ -19621,10 +19625,10 @@
         <v>716</v>
       </c>
       <c r="L144">
-        <v>72.206999999999994</v>
+        <v>23.386618958975088</v>
       </c>
       <c r="M144">
-        <v>0.14866872756951097</v>
+        <v>0.14871879671030974</v>
       </c>
       <c r="N144">
         <v>4</v>
@@ -19659,10 +19663,10 @@
         <v>716</v>
       </c>
       <c r="L145">
-        <v>77.007750000000001</v>
+        <v>32.70439896544066</v>
       </c>
       <c r="M145">
-        <v>0.14191512362774375</v>
+        <v>0.14221825477144187</v>
       </c>
       <c r="N145">
         <v>1</v>
@@ -19697,10 +19701,10 @@
         <v>716</v>
       </c>
       <c r="L146">
-        <v>79.141499999999994</v>
+        <v>28.448283149947585</v>
       </c>
       <c r="M146">
-        <v>0.14052697115389912</v>
+        <v>0.14061766327012626</v>
       </c>
       <c r="N146">
         <v>2</v>
@@ -19735,10 +19739,10 @@
         <v>716</v>
       </c>
       <c r="L147">
-        <v>75.312749999999994</v>
+        <v>23.5306691611204</v>
       </c>
       <c r="M147">
-        <v>0.1397831710646219</v>
+        <v>0.13974662706694277</v>
       </c>
       <c r="N147">
         <v>3</v>
@@ -19773,13 +19777,13 @@
         <v>716</v>
       </c>
       <c r="L148">
-        <v>63.779249999999998</v>
+        <v>21.906682612756555</v>
       </c>
       <c r="M148">
-        <v>0.13933527587135996</v>
+        <v>0.13921926257744968</v>
       </c>
       <c r="N148">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="2:14">
@@ -19811,13 +19815,13 @@
         <v>716</v>
       </c>
       <c r="L149">
-        <v>70.812749999999994</v>
+        <v>18.299983469384905</v>
       </c>
       <c r="M149">
-        <v>0.13920117215167685</v>
+        <v>0.13906938141911487</v>
       </c>
       <c r="N149">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="2:14">
@@ -19849,10 +19853,10 @@
         <v>716</v>
       </c>
       <c r="L150">
-        <v>95.180250000000001</v>
+        <v>30.458476825413882</v>
       </c>
       <c r="M150">
-        <v>0.13091183050444935</v>
+        <v>0.130924970752272</v>
       </c>
       <c r="N150">
         <v>3</v>
@@ -19887,10 +19891,10 @@
         <v>716</v>
       </c>
       <c r="L151">
-        <v>74.482500000000002</v>
+        <v>19.944156438715641</v>
       </c>
       <c r="M151">
-        <v>0.1306937089386313</v>
+        <v>0.13076342868396804</v>
       </c>
       <c r="N151">
         <v>5</v>
@@ -19925,10 +19929,10 @@
         <v>716</v>
       </c>
       <c r="L152">
-        <v>95.025000000000006</v>
+        <v>31.885803345821603</v>
       </c>
       <c r="M152">
-        <v>0.13002069481370601</v>
+        <v>0.13000593781731512</v>
       </c>
       <c r="N152">
         <v>2</v>
@@ -19963,10 +19967,10 @@
         <v>716</v>
       </c>
       <c r="L153">
-        <v>92.397000000000006</v>
+        <v>27.795953612125341</v>
       </c>
       <c r="M153">
-        <v>0.12979010147503178</v>
+        <v>0.12973185298744896</v>
       </c>
       <c r="N153">
         <v>4</v>
@@ -20001,10 +20005,10 @@
         <v>716</v>
       </c>
       <c r="L154">
-        <v>98.581500000000005</v>
+        <v>37.402505595329941</v>
       </c>
       <c r="M154">
-        <v>0.12887194797638071</v>
+        <v>0.12871562442587001</v>
       </c>
       <c r="N154">
         <v>1</v>
@@ -20039,10 +20043,10 @@
         <v>716</v>
       </c>
       <c r="L155">
-        <v>86.620500000000007</v>
+        <v>38.471974254388364</v>
       </c>
       <c r="M155">
-        <v>0.12103306036566462</v>
+        <v>0.12082642579605936</v>
       </c>
       <c r="N155">
         <v>1</v>
@@ -20077,10 +20081,10 @@
         <v>716</v>
       </c>
       <c r="L156">
-        <v>88.976249999999993</v>
+        <v>26.199691444836226</v>
       </c>
       <c r="M156">
-        <v>0.12069905567752204</v>
+        <v>0.12072454314267796</v>
       </c>
       <c r="N156">
         <v>3</v>
@@ -20115,10 +20119,10 @@
         <v>716</v>
       </c>
       <c r="L157">
-        <v>92.908500000000004</v>
+        <v>28.916805327721423</v>
       </c>
       <c r="M157">
-        <v>0.12023489600079171</v>
+        <v>0.12027335985708784</v>
       </c>
       <c r="N157">
         <v>2</v>
@@ -20153,10 +20157,10 @@
         <v>716</v>
       </c>
       <c r="L158">
-        <v>83.465999999999994</v>
+        <v>22.513686539218682</v>
       </c>
       <c r="M158">
-        <v>0.11992582225724005</v>
+        <v>0.11987112393904341</v>
       </c>
       <c r="N158">
         <v>4</v>
@@ -20191,10 +20195,10 @@
         <v>716</v>
       </c>
       <c r="L159">
-        <v>80.468249999999998</v>
+        <v>20.318072741238407</v>
       </c>
       <c r="M159">
-        <v>0.11826954988856227</v>
+        <v>0.11822162069789628</v>
       </c>
       <c r="N159">
         <v>5</v>
@@ -20229,10 +20233,10 @@
         <v>716</v>
       </c>
       <c r="L160">
-        <v>83.998500000000007</v>
+        <v>23.430992700860834</v>
       </c>
       <c r="M160">
-        <v>0.11132229469952412</v>
+        <v>0.11124392869883834</v>
       </c>
       <c r="N160">
         <v>4</v>
@@ -20267,10 +20271,10 @@
         <v>716</v>
       </c>
       <c r="L161">
-        <v>96.804000000000002</v>
+        <v>39.498281892272885</v>
       </c>
       <c r="M161">
-        <v>0.11049985829506</v>
+        <v>0.11044590145847795</v>
       </c>
       <c r="N161">
         <v>1</v>
@@ -20305,10 +20309,10 @@
         <v>716</v>
       </c>
       <c r="L162">
-        <v>94.454250000000002</v>
+        <v>33.135927880489099</v>
       </c>
       <c r="M162">
-        <v>0.10984493378827954</v>
+        <v>0.10991229098535622</v>
       </c>
       <c r="N162">
         <v>2</v>
@@ -20343,10 +20347,10 @@
         <v>716</v>
       </c>
       <c r="L163">
-        <v>92.183999999999997</v>
+        <v>27.802208317419165</v>
       </c>
       <c r="M163">
-        <v>0.10925749106303591</v>
+        <v>0.10942403254476314</v>
       </c>
       <c r="N163">
         <v>3</v>
@@ -20381,10 +20385,10 @@
         <v>716</v>
       </c>
       <c r="L164">
-        <v>64.740750000000006</v>
+        <v>15.893953378099724</v>
       </c>
       <c r="M164">
-        <v>0.10853484096848012</v>
+        <v>0.10854848382161991</v>
       </c>
       <c r="N164">
         <v>5</v>
@@ -20419,10 +20423,10 @@
         <v>716</v>
       </c>
       <c r="L165">
-        <v>86.749499999999998</v>
+        <v>24.865385243971481</v>
       </c>
       <c r="M165">
-        <v>0.10040232658496037</v>
+        <v>0.10050820452856439</v>
       </c>
       <c r="N165">
         <v>2</v>
@@ -20457,10 +20461,10 @@
         <v>716</v>
       </c>
       <c r="L166">
-        <v>64.95675</v>
+        <v>16.170008359753741</v>
       </c>
       <c r="M166">
-        <v>0.10023485759837619</v>
+        <v>0.10020144189206902</v>
       </c>
       <c r="N166">
         <v>4</v>
@@ -20495,10 +20499,10 @@
         <v>716</v>
       </c>
       <c r="L167">
-        <v>52.970999999999997</v>
+        <v>12.489291869954087</v>
       </c>
       <c r="M167">
-        <v>9.9811714648557176E-2</v>
+        <v>9.9803345380921477E-2</v>
       </c>
       <c r="N167">
         <v>5</v>
@@ -20533,10 +20537,10 @@
         <v>716</v>
       </c>
       <c r="L168">
-        <v>76.349249999999998</v>
+        <v>20.228568959680278</v>
       </c>
       <c r="M168">
-        <v>9.9707603708582754E-2</v>
+        <v>9.9682077720633727E-2</v>
       </c>
       <c r="N168">
         <v>3</v>
@@ -20571,10 +20575,10 @@
         <v>716</v>
       </c>
       <c r="L169">
-        <v>86.046750000000003</v>
+        <v>34.098102619112602</v>
       </c>
       <c r="M169">
-        <v>9.9677838570896793E-2</v>
+        <v>9.9263697055272215E-2</v>
       </c>
       <c r="N169">
         <v>1</v>
@@ -20609,10 +20613,10 @@
         <v>716</v>
       </c>
       <c r="L170">
-        <v>19.692</v>
+        <v>4.4982295184278458</v>
       </c>
       <c r="M170">
-        <v>9.1418835579730878E-2</v>
+        <v>9.1464018104620681E-2</v>
       </c>
       <c r="N170">
         <v>5</v>
@@ -20647,10 +20651,10 @@
         <v>716</v>
       </c>
       <c r="L171">
-        <v>32.35575</v>
+        <v>8.0599661115261068</v>
       </c>
       <c r="M171">
-        <v>9.12034921653153E-2</v>
+        <v>9.1237158090968176E-2</v>
       </c>
       <c r="N171">
         <v>4</v>
@@ -20685,10 +20689,10 @@
         <v>716</v>
       </c>
       <c r="L172">
-        <v>36.173250000000003</v>
+        <v>12.131358949409318</v>
       </c>
       <c r="M172">
-        <v>9.0908786509433834E-2</v>
+        <v>9.0747593194782775E-2</v>
       </c>
       <c r="N172">
         <v>2</v>
@@ -20723,13 +20727,13 @@
         <v>716</v>
       </c>
       <c r="L173">
-        <v>54.564</v>
+        <v>11.644900676532123</v>
       </c>
       <c r="M173">
-        <v>9.0808138768705929E-2</v>
+        <v>9.073938548517077E-2</v>
       </c>
       <c r="N173">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="2:14">
@@ -20761,13 +20765,13 @@
         <v>716</v>
       </c>
       <c r="L174">
-        <v>44.335500000000003</v>
+        <v>19.965539260459749</v>
       </c>
       <c r="M174">
-        <v>9.0770954328155032E-2</v>
+        <v>9.0556445610075004E-2</v>
       </c>
       <c r="N174">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="2:14">
@@ -20799,10 +20803,10 @@
         <v>716</v>
       </c>
       <c r="L175">
-        <v>29.7255</v>
+        <v>9.8403546271864961</v>
       </c>
       <c r="M175">
-        <v>8.1645827324705059E-2</v>
+        <v>8.1607004465746633E-2</v>
       </c>
       <c r="N175">
         <v>2</v>
@@ -20837,10 +20841,10 @@
         <v>716</v>
       </c>
       <c r="L176">
-        <v>35.31</v>
+        <v>8.7494874575949773</v>
       </c>
       <c r="M176">
-        <v>8.0348819858662282E-2</v>
+        <v>8.0330265781697635E-2</v>
       </c>
       <c r="N176">
         <v>4</v>
@@ -20875,10 +20879,10 @@
         <v>716</v>
       </c>
       <c r="L177">
-        <v>40.500749999999996</v>
+        <v>10.622979987847819</v>
       </c>
       <c r="M177">
-        <v>8.0055684905950733E-2</v>
+        <v>8.0085060019524562E-2</v>
       </c>
       <c r="N177">
         <v>3</v>
@@ -20913,10 +20917,10 @@
         <v>716</v>
       </c>
       <c r="L178">
-        <v>41.387250000000002</v>
+        <v>18.779523453742407</v>
       </c>
       <c r="M178">
-        <v>7.9290156609182955E-2</v>
+        <v>7.926675659711814E-2</v>
       </c>
       <c r="N178">
         <v>1</v>
@@ -20951,10 +20955,10 @@
         <v>716</v>
       </c>
       <c r="L179">
-        <v>10.0335</v>
+        <v>2.2771589228214726</v>
       </c>
       <c r="M179">
-        <v>7.8499860712621883E-2</v>
+        <v>7.8457988886176888E-2</v>
       </c>
       <c r="N179">
         <v>5</v>
@@ -20989,10 +20993,10 @@
         <v>716</v>
       </c>
       <c r="L180">
-        <v>19.908750000000001</v>
+        <v>5.4187148054351892</v>
       </c>
       <c r="M180">
-        <v>7.2349531048973306E-2</v>
+        <v>7.2392191091738459E-2</v>
       </c>
       <c r="N180">
         <v>2</v>
@@ -21027,10 +21031,10 @@
         <v>716</v>
       </c>
       <c r="L181">
-        <v>30.495750000000001</v>
+        <v>15.871913627885988</v>
       </c>
       <c r="M181">
-        <v>7.1414934278514752E-2</v>
+        <v>7.1355364411933866E-2</v>
       </c>
       <c r="N181">
         <v>1</v>
@@ -21065,10 +21069,10 @@
         <v>716</v>
       </c>
       <c r="L182">
-        <v>6.2257499999999997</v>
+        <v>1.4282497014192248</v>
       </c>
       <c r="M182">
-        <v>7.0227886297380998E-2</v>
+        <v>7.0218832843664869E-2</v>
       </c>
       <c r="N182">
         <v>5</v>
@@ -21103,10 +21107,10 @@
         <v>716</v>
       </c>
       <c r="L183">
-        <v>16.484249999999999</v>
+        <v>4.0004107934564352</v>
       </c>
       <c r="M183">
-        <v>6.99570896023686E-2</v>
+        <v>6.9929137580501538E-2</v>
       </c>
       <c r="N183">
         <v>4</v>
@@ -21141,10 +21145,10 @@
         <v>716</v>
       </c>
       <c r="L184">
-        <v>20.294250000000002</v>
+        <v>5.3055791084614183</v>
       </c>
       <c r="M184">
-        <v>6.8748115003796031E-2</v>
+        <v>6.8805094129738509E-2</v>
       </c>
       <c r="N184">
         <v>3</v>
@@ -21179,10 +21183,10 @@
         <v>716</v>
       </c>
       <c r="L185">
-        <v>10.431749999999999</v>
+        <v>2.8626811940488546</v>
       </c>
       <c r="M185">
-        <v>6.1520098178244366E-2</v>
+        <v>6.1561767483745262E-2</v>
       </c>
       <c r="N185">
         <v>3</v>
@@ -21217,10 +21221,10 @@
         <v>716</v>
       </c>
       <c r="L186">
-        <v>8.7352500000000006</v>
+        <v>2.1413277332033664</v>
       </c>
       <c r="M186">
-        <v>6.0987924414282232E-2</v>
+        <v>6.0997186771204241E-2</v>
       </c>
       <c r="N186">
         <v>5</v>
@@ -21255,10 +21259,10 @@
         <v>716</v>
       </c>
       <c r="L187">
-        <v>23.481000000000002</v>
+        <v>13.622920319972424</v>
       </c>
       <c r="M187">
-        <v>6.0476965159030671E-2</v>
+        <v>6.0085209309741816E-2</v>
       </c>
       <c r="N187">
         <v>1</v>
@@ -21293,10 +21297,10 @@
         <v>716</v>
       </c>
       <c r="L188">
-        <v>12.107250000000001</v>
+        <v>3.144766948266839</v>
       </c>
       <c r="M188">
-        <v>5.9484058717816861E-2</v>
+        <v>5.9483086102465652E-2</v>
       </c>
       <c r="N188">
         <v>4</v>
@@ -21331,10 +21335,10 @@
         <v>716</v>
       </c>
       <c r="L189">
-        <v>18.623999999999999</v>
+        <v>6.429226918978757</v>
       </c>
       <c r="M189">
-        <v>5.9300886422590196E-2</v>
+        <v>5.9247211714027373E-2</v>
       </c>
       <c r="N189">
         <v>2</v>
@@ -21369,10 +21373,10 @@
         <v>716</v>
       </c>
       <c r="L190">
-        <v>8.8417499999999993</v>
+        <v>3.6444684100455369</v>
       </c>
       <c r="M190">
-        <v>5.2253904147335682E-2</v>
+        <v>5.257202993294622E-2</v>
       </c>
       <c r="N190">
         <v>3</v>
@@ -21407,10 +21411,10 @@
         <v>716</v>
       </c>
       <c r="L191">
-        <v>13.365</v>
+        <v>3.9986407580264158</v>
       </c>
       <c r="M191">
-        <v>5.1923102811113481E-2</v>
+        <v>5.1947165861923543E-2</v>
       </c>
       <c r="N191">
         <v>2</v>
@@ -21445,10 +21449,10 @@
         <v>716</v>
       </c>
       <c r="L192">
-        <v>4.5570000000000004</v>
+        <v>1.2634645571967296</v>
       </c>
       <c r="M192">
-        <v>5.0538004947505918E-2</v>
+        <v>5.0557177830762759E-2</v>
       </c>
       <c r="N192">
         <v>4</v>
@@ -21483,10 +21487,10 @@
         <v>716</v>
       </c>
       <c r="L193">
-        <v>3.0667499999999999</v>
+        <v>0.80888711363471677</v>
       </c>
       <c r="M193">
-        <v>4.9393113761170483E-2</v>
+        <v>4.9423930312713603E-2</v>
       </c>
       <c r="N193">
         <v>5</v>
@@ -21521,10 +21525,10 @@
         <v>716</v>
       </c>
       <c r="L194">
-        <v>11.977499999999999</v>
+        <v>6.3619569419256718</v>
       </c>
       <c r="M194">
-        <v>4.8552321393488633E-2</v>
+        <v>4.8801296201976971E-2</v>
       </c>
       <c r="N194">
         <v>1</v>
@@ -21559,10 +21563,10 @@
         <v>716</v>
       </c>
       <c r="L195">
-        <v>1.347</v>
+        <v>0.37343330806890146</v>
       </c>
       <c r="M195">
-        <v>4.4260669303409633E-2</v>
+        <v>4.4259899314931739E-2</v>
       </c>
       <c r="N195">
         <v>4</v>
@@ -21597,10 +21601,10 @@
         <v>716</v>
       </c>
       <c r="L196">
-        <v>1.635</v>
+        <v>0.45569355172093096</v>
       </c>
       <c r="M196">
-        <v>4.1932368441266028E-2</v>
+        <v>4.1901936715876102E-2</v>
       </c>
       <c r="N196">
         <v>3</v>
@@ -21635,10 +21639,10 @@
         <v>716</v>
       </c>
       <c r="L197">
-        <v>3.3247499999999999</v>
+        <v>0.9397596712805828</v>
       </c>
       <c r="M197">
-        <v>4.0027199586739434E-2</v>
+        <v>4.0064807567141467E-2</v>
       </c>
       <c r="N197">
         <v>2</v>
@@ -21673,10 +21677,10 @@
         <v>716</v>
       </c>
       <c r="L198">
-        <v>6.4117499999999996</v>
+        <v>2.1091736918199375</v>
       </c>
       <c r="M198">
-        <v>3.8153653652546277E-2</v>
+        <v>3.8099693728236919E-2</v>
       </c>
       <c r="N198">
         <v>1</v>
@@ -21711,10 +21715,10 @@
         <v>716</v>
       </c>
       <c r="L199">
-        <v>1.8314999999999999</v>
+        <v>0.46921348856207579</v>
       </c>
       <c r="M199">
-        <v>3.7013317361749051E-2</v>
+        <v>3.70128727314201E-2</v>
       </c>
       <c r="N199">
         <v>5</v>
@@ -21749,10 +21753,10 @@
         <v>716</v>
       </c>
       <c r="L200">
-        <v>2.03925</v>
+        <v>0.59616752638056714</v>
       </c>
       <c r="M200">
-        <v>3.080585827398118E-2</v>
+        <v>3.0740265533582004E-2</v>
       </c>
       <c r="N200">
         <v>2</v>
@@ -21787,10 +21791,10 @@
         <v>716</v>
       </c>
       <c r="L201">
-        <v>10.569000000000001</v>
+        <v>6.6937974295285807</v>
       </c>
       <c r="M201">
-        <v>3.0556005626461481E-2</v>
+        <v>3.0682931543918254E-2</v>
       </c>
       <c r="N201">
         <v>1</v>
@@ -21825,10 +21829,10 @@
         <v>716</v>
       </c>
       <c r="L202">
-        <v>1.1685000000000001</v>
+        <v>0.32897350145868881</v>
       </c>
       <c r="M202">
-        <v>3.0401805811397113E-2</v>
+        <v>3.0406363368380138E-2</v>
       </c>
       <c r="N202">
         <v>3</v>
@@ -21863,10 +21867,10 @@
         <v>716</v>
       </c>
       <c r="L203">
-        <v>2.5575000000000001</v>
+        <v>0.73067218503398279</v>
       </c>
       <c r="M203">
-        <v>2.7948270688557479E-2</v>
+        <v>2.7952551011926324E-2</v>
       </c>
       <c r="N203">
         <v>4</v>
@@ -21901,10 +21905,10 @@
         <v>716</v>
       </c>
       <c r="L204">
-        <v>0.13575000000000001</v>
+        <v>3.5834868447911145E-2</v>
       </c>
       <c r="M204">
-        <v>2.7645992033804669E-2</v>
+        <v>2.7682330368412483E-2</v>
       </c>
       <c r="N204">
         <v>5</v>
@@ -21939,10 +21943,10 @@
         <v>716</v>
       </c>
       <c r="L205">
-        <v>2.6692499999999999</v>
+        <v>0.89671761476202783</v>
       </c>
       <c r="M205">
-        <v>2.0836309346533077E-2</v>
+        <v>2.0987075356200965E-2</v>
       </c>
       <c r="N205">
         <v>2</v>
@@ -21977,10 +21981,10 @@
         <v>716</v>
       </c>
       <c r="L206">
-        <v>0.86399999999999999</v>
+        <v>0.3456072694565217</v>
       </c>
       <c r="M206">
-        <v>1.9973212979706608E-2</v>
+        <v>1.9963935347450387E-2</v>
       </c>
       <c r="N206">
         <v>1</v>
@@ -22015,10 +22019,10 @@
         <v>716</v>
       </c>
       <c r="L207">
-        <v>1.3514999999999999</v>
+        <v>0.35477071023706153</v>
       </c>
       <c r="M207">
-        <v>1.8376861858562472E-2</v>
+        <v>1.8380166078989801E-2</v>
       </c>
       <c r="N207">
         <v>4</v>
@@ -22053,10 +22057,10 @@
         <v>716</v>
       </c>
       <c r="L208">
-        <v>0.75149999999999995</v>
+        <v>0.37294861915650235</v>
       </c>
       <c r="M208">
-        <v>1.7408103064672671E-2</v>
+        <v>1.669129581379284E-2</v>
       </c>
       <c r="N208">
         <v>3</v>
@@ -22091,10 +22095,10 @@
         <v>716</v>
       </c>
       <c r="L209">
-        <v>0.61875000000000002</v>
+        <v>0.15701588770115982</v>
       </c>
       <c r="M209">
-        <v>1.5439407943316337E-2</v>
+        <v>1.5438828349766344E-2</v>
       </c>
       <c r="N209">
         <v>5</v>
@@ -22129,10 +22133,10 @@
         <v>716</v>
       </c>
       <c r="L210">
-        <v>2.5185</v>
+        <v>1.5127421104721952</v>
       </c>
       <c r="M210">
-        <v>1.1151017390186025E-2</v>
+        <v>1.1351134049785523E-2</v>
       </c>
       <c r="N210">
         <v>2</v>
@@ -22167,10 +22171,10 @@
         <v>716</v>
       </c>
       <c r="L211">
-        <v>1.143</v>
+        <v>0.56782629978714427</v>
       </c>
       <c r="M211">
-        <v>1.0417016943182585E-2</v>
+        <v>1.0260221537453915E-2</v>
       </c>
       <c r="N211">
         <v>3</v>
@@ -22205,10 +22209,10 @@
         <v>716</v>
       </c>
       <c r="L212">
-        <v>1.131</v>
+        <v>0.45185584145469632</v>
       </c>
       <c r="M212">
-        <v>1.0164185768973873E-2</v>
+        <v>9.1492920021549688E-3</v>
       </c>
       <c r="N212">
         <v>5</v>
@@ -22243,10 +22247,10 @@
         <v>716</v>
       </c>
       <c r="L213">
-        <v>2.2035</v>
+        <v>1.1766237133213684</v>
       </c>
       <c r="M213">
-        <v>9.7859338000114895E-3</v>
+        <v>8.689147815374448E-3</v>
       </c>
       <c r="N213">
         <v>1</v>
@@ -22281,10 +22285,10 @@
         <v>716</v>
       </c>
       <c r="L214">
-        <v>1.0117499999999999</v>
+        <v>0.63230831338795723</v>
       </c>
       <c r="M214">
-        <v>8.7298919234972041E-3</v>
+        <v>8.5242728378872694E-3</v>
       </c>
       <c r="N214">
         <v>4</v>
@@ -22319,10 +22323,10 @@
         <v>716</v>
       </c>
       <c r="L215">
-        <v>0.98099999999999998</v>
+        <v>0.608209065446773</v>
       </c>
       <c r="M215">
-        <v>2.2332342246201603E-3</v>
+        <v>2.090788031027298E-3</v>
       </c>
       <c r="N215">
         <v>2</v>
@@ -22357,10 +22361,10 @@
         <v>716</v>
       </c>
       <c r="L216">
-        <v>0.62250000000000005</v>
+        <v>0.48371757229742274</v>
       </c>
       <c r="M216">
-        <v>2.0346196310913442E-3</v>
+        <v>1.8586243460675281E-3</v>
       </c>
       <c r="N216">
         <v>1</v>
@@ -22395,10 +22399,10 @@
         <v>716</v>
       </c>
       <c r="L217">
-        <v>0.19425000000000001</v>
+        <v>0.13653705801931076</v>
       </c>
       <c r="M217">
-        <v>1.7903116989606363E-3</v>
+        <v>1.8331667659071038E-3</v>
       </c>
       <c r="N217">
         <v>5</v>
@@ -22433,10 +22437,10 @@
         <v>716</v>
       </c>
       <c r="L218">
-        <v>0.3105</v>
+        <v>0.11381809091109378</v>
       </c>
       <c r="M218">
-        <v>1.6600431022853743E-3</v>
+        <v>1.3843571703413282E-3</v>
       </c>
       <c r="N218">
         <v>4</v>
@@ -22471,10 +22475,10 @@
         <v>716</v>
       </c>
       <c r="L219">
-        <v>0.38700000000000001</v>
+        <v>0.23325247662257453</v>
       </c>
       <c r="M219">
-        <v>1.5417542318265276E-3</v>
+        <v>1.369107830085393E-3</v>
       </c>
       <c r="N219">
         <v>3</v>
@@ -22486,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4F4EFD2-D1F9-45C7-8118-9F2D4E8D3FD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B2E44C-662D-422E-85C4-4E37EBB6A084}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{031D0189-49EB-4FFF-A3D2-95267C367B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76482F8-A82C-49CC-85D2-8CBF68D7F219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,34 +979,34 @@
     <t>solar resource -- CF class spv-IND_16 -- cost class 4</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c3</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
   </si>
   <si>
-    <t>e_spv-IND_0_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_spv-IND_0_c4</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
   </si>
   <si>
     <t>comm-out</t>
@@ -7950,7 +7950,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE42652-1440-4710-B690-CA44501A8F26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A33852-C79D-4A74-9686-786AEBE80038}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9891,13 +9891,13 @@
         <v>297</v>
       </c>
       <c r="L60">
-        <v>0.77364403067522491</v>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -9929,13 +9929,13 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>3.2726001779475915</v>
+        <v>5.3282119260176248</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -9967,13 +9967,13 @@
         <v>297</v>
       </c>
       <c r="L62">
-        <v>4.4778378857750975E-2</v>
+        <v>3.2726001779475915</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -10005,13 +10005,13 @@
         <v>297</v>
       </c>
       <c r="L63">
-        <v>5.2500000000000003E-3</v>
+        <v>0.77364403067522491</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -10043,13 +10043,13 @@
         <v>297</v>
       </c>
       <c r="L64">
-        <v>5.3282119260176248</v>
+        <v>4.4778378857750975E-2</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10058,7 +10058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD131F0-1802-4537-848C-C6BD234EBE9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41D5BEC-9FC1-41AA-9D97-9CCDCF1CDEE5}">
   <dimension ref="B9:AB219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22490,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B2E44C-662D-422E-85C4-4E37EBB6A084}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F588028C-2F7B-45D9-8674-918C54C9EE71}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76482F8-A82C-49CC-85D2-8CBF68D7F219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DAC02A2-2084-40C5-8FE0-D62B067D3B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,6 +979,12 @@
     <t>solar resource -- CF class spv-IND_16 -- cost class 4</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c5</t>
   </si>
   <si>
@@ -989,12 +995,6 @@
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
   </si>
   <si>
     <t>e_spv-IND_0_c3</t>
@@ -7950,7 +7950,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A33852-C79D-4A74-9686-786AEBE80038}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5004431C-2AE8-4E45-940C-8EC85C3C166F}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9891,13 +9891,13 @@
         <v>297</v>
       </c>
       <c r="L60">
-        <v>5.2500000000000003E-3</v>
+        <v>3.2726001779475915</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -9929,13 +9929,13 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>5.3282119260176248</v>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -9967,13 +9967,13 @@
         <v>297</v>
       </c>
       <c r="L62">
-        <v>3.2726001779475915</v>
+        <v>5.3282119260176248</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -10058,7 +10058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41D5BEC-9FC1-41AA-9D97-9CCDCF1CDEE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A5721E-0D5F-4C2D-B180-1B46C55EF90C}">
   <dimension ref="B9:AB219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22490,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F588028C-2F7B-45D9-8674-918C54C9EE71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F77C4C-A962-46D0-A458-DA32111059A7}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DAC02A2-2084-40C5-8FE0-D62B067D3B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2F70220-2914-4988-BEC0-72D2F16B26B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,34 +979,34 @@
     <t>solar resource -- CF class spv-IND_16 -- cost class 4</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c3</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c1</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c5</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c3</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
   </si>
   <si>
     <t>comm-out</t>
@@ -7950,7 +7950,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5004431C-2AE8-4E45-940C-8EC85C3C166F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B04CBC-D2F7-444D-8528-01CE92E6E380}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9891,13 +9891,13 @@
         <v>297</v>
       </c>
       <c r="L60">
-        <v>3.2726001779475915</v>
+        <v>5.3282119260176248</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -9929,13 +9929,13 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>5.2500000000000003E-3</v>
+        <v>0.77364403067522491</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -9967,13 +9967,13 @@
         <v>297</v>
       </c>
       <c r="L62">
-        <v>5.3282119260176248</v>
+        <v>3.2726001779475915</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -10005,13 +10005,13 @@
         <v>297</v>
       </c>
       <c r="L63">
-        <v>0.77364403067522491</v>
+        <v>4.4778378857750975E-2</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -10043,13 +10043,13 @@
         <v>297</v>
       </c>
       <c r="L64">
-        <v>4.4778378857750975E-2</v>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10058,7 +10058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A5721E-0D5F-4C2D-B180-1B46C55EF90C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FDD5A5-A00E-4D2B-9FFA-68AEFC2D1BA3}">
   <dimension ref="B9:AB219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22490,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F77C4C-A962-46D0-A458-DA32111059A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567932EE-9D4A-48C3-89FD-083F1952C802}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2F70220-2914-4988-BEC0-72D2F16B26B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91C669C6-B10F-466B-AF7E-15EBB01CFAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,6 +979,18 @@
     <t>solar resource -- CF class spv-IND_16 -- cost class 4</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c2</t>
   </si>
   <si>
@@ -991,22 +1003,10 @@
     <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
   </si>
   <si>
-    <t>e_spv-IND_0_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_spv-IND_0_c4</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
   </si>
   <si>
     <t>comm-out</t>
@@ -7950,7 +7950,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B04CBC-D2F7-444D-8528-01CE92E6E380}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B32914F-268D-4591-BE85-95323F3E4F06}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9891,13 +9891,13 @@
         <v>297</v>
       </c>
       <c r="L60">
-        <v>5.3282119260176248</v>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -9929,13 +9929,13 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>0.77364403067522491</v>
+        <v>3.2726001779475915</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -9967,13 +9967,13 @@
         <v>297</v>
       </c>
       <c r="L62">
-        <v>3.2726001779475915</v>
+        <v>5.3282119260176248</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -10005,13 +10005,13 @@
         <v>297</v>
       </c>
       <c r="L63">
-        <v>4.4778378857750975E-2</v>
+        <v>0.77364403067522491</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -10043,13 +10043,13 @@
         <v>297</v>
       </c>
       <c r="L64">
-        <v>5.2500000000000003E-3</v>
+        <v>4.4778378857750975E-2</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10058,7 +10058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FDD5A5-A00E-4D2B-9FFA-68AEFC2D1BA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59CA7D7-36B7-494E-83FE-3A07D89ADEAE}">
   <dimension ref="B9:AB219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22490,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567932EE-9D4A-48C3-89FD-083F1952C802}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D288BBC1-6B0B-4A32-B1B3-12CEA2941353}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91C669C6-B10F-466B-AF7E-15EBB01CFAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D17198F-CFFA-4CB1-A4FA-638DCA5E1A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,6 +979,18 @@
     <t>solar resource -- CF class spv-IND_16 -- cost class 4</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c5</t>
   </si>
   <si>
@@ -991,22 +1003,10 @@
     <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
   </si>
   <si>
-    <t>e_spv-IND_0_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_spv-IND_0_c3</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
   </si>
   <si>
     <t>comm-out</t>
@@ -7950,7 +7950,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B32914F-268D-4591-BE85-95323F3E4F06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3DB30B-2552-4D72-A327-35228E516C70}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9891,13 +9891,13 @@
         <v>297</v>
       </c>
       <c r="L60">
-        <v>5.2500000000000003E-3</v>
+        <v>5.3282119260176248</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -9929,13 +9929,13 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>3.2726001779475915</v>
+        <v>4.4778378857750975E-2</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -9967,13 +9967,13 @@
         <v>297</v>
       </c>
       <c r="L62">
-        <v>5.3282119260176248</v>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -10005,13 +10005,13 @@
         <v>297</v>
       </c>
       <c r="L63">
-        <v>0.77364403067522491</v>
+        <v>3.2726001779475915</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -10043,13 +10043,13 @@
         <v>297</v>
       </c>
       <c r="L64">
-        <v>4.4778378857750975E-2</v>
+        <v>0.77364403067522491</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10058,7 +10058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59CA7D7-36B7-494E-83FE-3A07D89ADEAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E06FEC-01C7-4C1E-B1A8-465436E350A5}">
   <dimension ref="B9:AB219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22490,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D288BBC1-6B0B-4A32-B1B3-12CEA2941353}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3CE1D0-0606-479C-A9D2-D5527A2F367F}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D17198F-CFFA-4CB1-A4FA-638DCA5E1A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E1837F8-3CB9-4CC2-9428-D97A5072FD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,34 +979,34 @@
     <t>solar resource -- CF class spv-IND_16 -- cost class 4</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c3</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_spv-IND_0_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c2</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c3</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
   </si>
   <si>
     <t>comm-out</t>
@@ -7950,7 +7950,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3DB30B-2552-4D72-A327-35228E516C70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{111F68D9-CD61-461F-8069-AA54A5CA7695}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9891,13 +9891,13 @@
         <v>297</v>
       </c>
       <c r="L60">
-        <v>5.3282119260176248</v>
+        <v>3.2726001779475915</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -9929,13 +9929,13 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>4.4778378857750975E-2</v>
+        <v>0.77364403067522491</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -10005,13 +10005,13 @@
         <v>297</v>
       </c>
       <c r="L63">
-        <v>3.2726001779475915</v>
+        <v>4.4778378857750975E-2</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -10043,13 +10043,13 @@
         <v>297</v>
       </c>
       <c r="L64">
-        <v>0.77364403067522491</v>
+        <v>5.3282119260176248</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -10058,7 +10058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E06FEC-01C7-4C1E-B1A8-465436E350A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8434CE1D-7DB1-4727-92F0-5DEAA8071B1F}">
   <dimension ref="B9:AB219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22490,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3CE1D0-0606-479C-A9D2-D5527A2F367F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D855002-F526-4F56-96F4-F72BE6D1AF89}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E1837F8-3CB9-4CC2-9428-D97A5072FD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44FC1C4C-C609-4EC5-B48A-7E0320C9A247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -985,16 +985,16 @@
     <t>solar resource -- CF class spv-IND_0 -- cost class 1</t>
   </si>
   <si>
+    <t>e_spv-IND_0_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_spv-IND_0_c3</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-IND_0 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-IND_0_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-IND_0 -- cost class 5</t>
   </si>
   <si>
     <t>e_spv-IND_0_c4</t>
@@ -7950,7 +7950,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{111F68D9-CD61-461F-8069-AA54A5CA7695}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C225FDC7-0641-4A47-A973-3FCD4D0BB948}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9929,13 +9929,13 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>0.77364403067522491</v>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -9967,13 +9967,13 @@
         <v>297</v>
       </c>
       <c r="L62">
-        <v>5.2500000000000003E-3</v>
+        <v>0.77364403067522491</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -10058,7 +10058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8434CE1D-7DB1-4727-92F0-5DEAA8071B1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4F1ABE-1914-4A1B-80C9-12DE77C254E0}">
   <dimension ref="B9:AB219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22490,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D855002-F526-4F56-96F4-F72BE6D1AF89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FAC20D-4FED-43E8-A04B-C7117D731F6B}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
